--- a/anthropic/docs/reports/20261022_v0.1.3-A_對照.xlsx
+++ b/anthropic/docs/reports/20261022_v0.1.3-A_對照.xlsx
@@ -519,7 +519,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>對照（U2）：Lambda 揭露 MW ÷ 1000 vs 模型 Lambda 供給 GW（金額回推；D 欄＝揭露，E–I＝模型）</t>
+          <t>供給 GW（U2 新法）：Nscale Monarch＝揭露 MW ÷ 1000 × IT 換算 × 爬坡 × 期間</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -527,27 +527,27 @@
           <t>GW</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>0.35</v>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="3" t="n">
-        <v>0.175</v>
+      <c r="G2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.35</v>
+        <v>0.23</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.35</v>
+        <v>0.46</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.35</v>
+        <v>0.46</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>D10：GW 由金額回推並與既有揭露 GW 對照（不校準）</t>
+          <t>揭露容量（SRC_ANT 的 MW，Verified／Interested-party）；期間＝Inputs 起始年至結束年（U2）；u2_method＝1 時進入供給</t>
         </is>
       </c>
     </row>
@@ -564,25 +564,35 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>對照（U2）：Lambda 模型峰值 GW ÷ 揭露 GW</t>
+          <t>供給 GW（U2 新法）：Lambda＝揭露 MW ÷ 1000 × IT 換算 × 爬坡 × 期間</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>倍</t>
+          <t>GW</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0.35</v>
+      </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>&gt; 1＝金額回推的 GW 大於揭露（合約價 12 偏低或『最高 86』含未計容量）</t>
+          <t>揭露容量（SRC_ANT 的 MW，Verified／Interested-party）；期間＝Inputs 起始年至結束年（U2）；u2_method＝1 時進入供給</t>
         </is>
       </c>
     </row>
@@ -9622,7 +9632,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>計入則第 1 層缺口縮小約 20.3</t>
+          <t>計入則第 1 層起算現金多 20.28，累計外部資金需求最多減少同額</t>
         </is>
       </c>
     </row>

--- a/anthropic/docs/reports/20261022_v0.1.3-A_對照.xlsx
+++ b/anthropic/docs/reports/20261022_v0.1.3-A_對照.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K179"/>
+  <dimension ref="A1:K182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -609,7 +609,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>U2 年付款上限：Nscale Monarch＝錨定總額 ÷ Σ 爬坡權重 × 當年權重</t>
+          <t>U2 年付款：Nscale Monarch＝錨定總額 ÷ Σ 爬坡權重 × 當年權重</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>v0.1.1 的付款時程（金額型）即此列；新法以它為上限，揭露容量 × 合約價較低時取較低者</t>
+          <t>即合約實付（u2_switch＝1）；新舊法付款相同</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>U2 年付款上限：Lambda＝錨定總額 ÷ Σ 爬坡權重 × 當年權重</t>
+          <t>U2 年付款：Lambda＝錨定總額 ÷ Σ 爬坡權重 × 當年權重</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>v0.1.1 的付款時程（金額型）即此列；新法以它為上限，揭露容量 × 合約價較低時取較低者</t>
+          <t>即合約實付（u2_switch＝1）；新舊法付款相同</t>
         </is>
       </c>
     </row>
@@ -699,35 +699,25 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>U2 新法：年上限實際約束的合約年數（揭露 GW × 合約價 &gt; 年上限）</t>
+          <t>隱含每 GW 年付款（Nscale）＝峰值年付款 ÷ 揭露容量 GW（對照；通用合約價 12 × 持有比）</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>年數</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>0</v>
-      </c>
+          <t>$B/GW/年</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>19.304152637486</v>
+      </c>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0＝兩約付款都由揭露容量決定（未被 86 約束）</t>
+          <t>對照用：高於通用合約價 → 金額 86 含揭露 GW 以外的容量或服務</t>
         </is>
       </c>
     </row>
@@ -744,35 +734,25 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>U2 新法 − v0.1.1：Nscale＋Lambda 合約實付差（新法開啟時；$B）</t>
+          <t>隱含每 GW 年付款（Lambda）＝峰值年付款 ÷ 揭露容量 GW（對照；通用合約價 12 × 持有比）</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>$B</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>-0.377366255144033</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>-2.43468761690984</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>-4.11464272353161</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>-4.11464272353161</v>
-      </c>
+          <t>$B/GW/年</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>14.156378600823</v>
+      </c>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>＝新法付款 − 年上限（v0.1.1 付款）；≤ 0</t>
+          <t>對照用：高於通用合約價 → 金額 86 含揭露 GW 以外的容量或服務</t>
         </is>
       </c>
     </row>
@@ -789,32 +769,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>U2 新法檢查：付款 − 年上限 的正部分，及付款 − 揭露 GW × 合約價 的正部分（合計；應為 0）</t>
+          <t>隱含每 GW 年付款（兩約合計）＝兩約峰值年付款 ÷ 兩約揭露容量</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>$B</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>0</v>
-      </c>
+          <t>$B/GW/年</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>17.0798058315205</v>
+      </c>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
       <c r="K8" s="2" t="n"/>
     </row>
     <row r="9">
@@ -830,7 +800,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>追加合約滿載年付款＝比例 × 當年基準合約付款（追加年內；Inputs）</t>
+          <t>U2 檢查：合約實付 − 年付款列（u2_switch＝1 時；各年絕對差合計；應為 0）</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -850,17 +820,13 @@
       <c r="H9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="3" t="n">
-        <v>27.9421131149552</v>
-      </c>
-      <c r="J9" s="3" t="n">
-        <v>26.4421131149552</v>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>Assumed（區間 0–60%）；基準模型不追加</t>
-        </is>
-      </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -875,7 +841,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>追加合約實付（各批依爬坡年數爬坡後加總）</t>
+          <t>追加合約滿載年付款＝比例 × 當年基準合約付款（追加年內；Inputs）</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -896,14 +862,14 @@
         <v>0</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>13.9710565574776</v>
+        <v>29.1765059320147</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>41.1631696724328</v>
+        <v>27.6765059320147</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>各批付款 × MIN(爬坡年數, 已過年數) ÷ 爬坡年數（同金額型合約）；合約價沿用既有</t>
+          <t>Assumed（區間 0–60%）；基準模型不追加</t>
         </is>
       </c>
     </row>
@@ -920,12 +886,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>追加供給 GW＝追加實付 ÷ VR200 族合約價</t>
+          <t>追加合約實付（各批依爬坡年數爬坡後加總）</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>$B</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -941,14 +907,14 @@
         <v>0</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1.16425471312313</v>
+        <v>14.5882529660074</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>3.4302641393694</v>
+        <v>43.0147588980221</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D10：GW＝金額 ÷ 合約價；新簽 → VR200 世代（同 U6）</t>
+          <t>各批付款 × MIN(爬坡年數, 已過年數) ÷ 爬坡年數（同金額型合約）；合約價沿用既有</t>
         </is>
       </c>
     </row>
@@ -965,7 +931,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>供給 VR 等值 GW（含追加）</t>
+          <t>追加供給 GW＝追加實付 ÷ VR200 族合約價</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -973,25 +939,29 @@
           <t>GW</t>
         </is>
       </c>
-      <c r="E12" s="3" t="n">
-        <v>0.0578024697954382</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>1.07470023516865</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>4.60959697168135</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>7.3818779368854</v>
+      <c r="E12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>8.95356941240637</v>
+        <v>1.21568774716728</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>11.1756440048576</v>
-      </c>
-      <c r="K12" s="2" t="n"/>
+        <v>3.58456324150184</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>D10：GW＝金額 ÷ 合約價；新簽 → VR200 世代（同 U6）</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1006,31 +976,31 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>算力成本（含追加）</t>
+          <t>供給 VR 等值 GW（含追加）</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>$B</t>
+          <t>GW</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7.33</v>
+        <v>0.0578024697954382</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>42.4201685560054</v>
+        <v>1.07470023516865</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>86.31145708093079</v>
+        <v>4.60959697168135</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>117.047043716517</v>
+        <v>7.3818779368854</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>107.111433607328</v>
+        <v>9.00500244645052</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>129.303546722284</v>
+        <v>11.3299431069901</v>
       </c>
       <c r="K13" s="2" t="n"/>
     </row>
@@ -1047,7 +1017,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>追加營收（無需求）＝變現比例 × 追加 VR 等值 GW × 當年基準每 VR 等值 GW 營收淨額</t>
+          <t>算力成本（含追加）</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1055,29 +1025,25 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>完全變現＝新增 GW 的每 GW 營收等於當年基準每 VR 等值 GW 營收淨額（工作單）</t>
-        </is>
-      </c>
+      <c r="E14" s="3" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>42.4201685560054</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>86.6888233360748</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>119.481731333427</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>111.84327273939</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>135.269778671404</v>
+      </c>
+      <c r="K14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1092,35 +1058,35 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>每 VR 等值 GW 差額（含股權報酬；追加情境：無需求）</t>
+          <t>追加營收（無需求）＝變現比例 × 追加 VR 等值 GW × 當年基準每 VR 等值 GW 營收淨額</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>$B/GW/年</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>-139.267405501682</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>-5.36501172129409</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>-4.82838767297759</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>-2.36820322078252</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>3.57869294486578</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>4.72569908457296</v>
+          <t>$B</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>＝（基準差額 ＋ 追加營收 − 追加實付）÷（基準＋追加 VR 等值 GW）</t>
+          <t>完全變現＝新增 GW 的每 GW 營收等於當年基準每 VR 等值 GW 營收淨額（工作單）</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1103,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>差：追加情境（無需求）− 基準（每 VR 等值 GW 差額）</t>
+          <t>每 VR 等值 GW 差額（含股權報酬；追加情境：無需求）</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1145,25 +1111,29 @@
           <t>$B/GW/年</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>0</v>
+      <c r="E16" s="3" t="n">
+        <v>-139.267405501682</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-5.36501172129409</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>-4.91025301987502</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>-2.69802276504026</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-2.32851892439615</v>
+        <v>3.03278502342309</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-7.40745667379579</v>
-      </c>
-      <c r="K16" s="2" t="n"/>
+        <v>4.13475145036218</v>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>＝（基準差額 ＋ 追加營收 − 追加實付）÷（基準＋追加 VR 等值 GW）</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1178,37 +1148,33 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>覆蓋率（追加情境：無需求）</t>
+          <t>差：追加情境（無需求）− 基準（每 VR 等值 GW 差額）</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>倍</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>0.345475241889585</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>0.888124307888594</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>0.773801380995813</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>0.867395652649717</v>
+          <t>$B/GW/年</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1.25745745936383</v>
+        <v>-2.34618490384743</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>1.35500391456511</v>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>營收淨額 ÷ 全成本（含股權報酬）</t>
-        </is>
-      </c>
+        <v>-7.46716597044412</v>
+      </c>
+      <c r="K17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1223,35 +1189,35 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>自由現金流（追加情境：無需求）</t>
+          <t>覆蓋率（追加情境：無需求）</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>$B</t>
+          <t>倍</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>-6.2848</v>
+        <v>0.345475241889585</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>-2.58841935855733</v>
+        <v>0.888124307888594</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>-18.1263531954611</v>
+        <v>0.770845036748019</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>-12.5251055055554</v>
+        <v>0.851667231837521</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>37.7422595275447</v>
+        <v>1.21139975474192</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>59.0829328672689</v>
+        <v>1.30275729846968</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Funding 第十節</t>
+          <t>營收淨額 ÷ 全成本（含股權報酬）</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1234,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>追加營收（部分變現）＝變現比例 × 追加 VR 等值 GW × 當年基準每 VR 等值 GW 營收淨額</t>
+          <t>自由現金流（追加情境：無需求）</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1276,27 +1242,27 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>0</v>
+      <c r="E19" s="3" t="n">
+        <v>-6.2848</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>-2.58841935855733</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>-18.5037194506051</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>-14.9597931224653</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>11.6957270123871</v>
+        <v>33.0104203954834</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>44.6376041095364</v>
+        <v>53.1167009181481</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>完全變現＝新增 GW 的每 GW 營收等於當年基準每 VR 等值 GW 營收淨額（工作單）</t>
+          <t>Funding 第十節</t>
         </is>
       </c>
     </row>
@@ -1313,35 +1279,35 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>每 VR 等值 GW 差額（含股權報酬；追加情境：部分變現）</t>
+          <t>追加營收（部分變現）＝變現比例 × 追加 VR 等值 GW × 當年基準每 VR 等值 GW 營收淨額</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>$B/GW/年</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>-139.267405501682</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>-5.36501172129409</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>-4.82838767297759</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>-2.36820322078252</v>
+          <t>$B</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>4.88495712551547</v>
+        <v>12.2124066691827</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>8.719885378457599</v>
+        <v>46.645479292207</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>＝（基準差額 ＋ 追加營收 − 追加實付）÷（基準＋追加 VR 等值 GW）</t>
+          <t>完全變現＝新增 GW 的每 GW 營收等於當年基準每 VR 等值 GW 營收淨額（工作單）</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1324,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>差：追加情境（部分變現）− 基準（每 VR 等值 GW 差額）</t>
+          <t>每 VR 等值 GW 差額（含股權報酬；追加情境：部分變現）</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1366,25 +1332,29 @@
           <t>$B/GW/年</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>0</v>
+      <c r="E21" s="3" t="n">
+        <v>-139.267405501682</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>-5.36501172129409</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>-4.91025301987502</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>-2.69802276504026</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-1.02225474374647</v>
+        <v>4.3889652956446</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-3.41327037991115</v>
-      </c>
-      <c r="K21" s="2" t="n"/>
+        <v>8.251760587277341</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>＝（基準差額 ＋ 追加營收 − 追加實付）÷（基準＋追加 VR 等值 GW）</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1399,37 +1369,33 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>覆蓋率（追加情境：部分變現）</t>
+          <t>差：追加情境（部分變現）− 基準（每 VR 等值 GW 差額）</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>倍</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>0.345475241889585</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>0.888124307888594</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>0.773801380995813</v>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>0.867395652649717</v>
+          <t>$B/GW/年</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>1.35143240004448</v>
+        <v>-0.990004631625918</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1.65505513332769</v>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>營收淨額 ÷ 全成本（含股權報酬）</t>
-        </is>
-      </c>
+        <v>-3.35015683352896</v>
+      </c>
+      <c r="K22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1444,35 +1410,35 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>自由現金流（追加情境：部分變現）</t>
+          <t>覆蓋率（追加情境：部分變現）</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>$B</t>
+          <t>倍</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-6.2848</v>
+        <v>0.345475241889585</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-2.58841935855733</v>
+        <v>0.888124307888594</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-18.1263531954611</v>
+        <v>0.770845036748019</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>-12.5251055055554</v>
+        <v>0.851667231837521</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>49.4379865399318</v>
+        <v>1.30593206570996</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>103.720536976805</v>
+        <v>1.60421545841741</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Funding 第十節</t>
+          <t>營收淨額 ÷ 全成本（含股權報酬）</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1455,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>追加營收（完全變現）＝變現比例 × 追加 VR 等值 GW × 當年基準每 VR 等值 GW 營收淨額</t>
+          <t>自由現金流（追加情境：部分變現）</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1497,27 +1463,27 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>0</v>
+      <c r="E24" s="3" t="n">
+        <v>-6.2848</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>-2.58841935855733</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>-18.5037194506051</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>-14.9597931224653</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>23.3914540247741</v>
+        <v>45.222827064666</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>89.27520821907289</v>
+        <v>99.7621802103551</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>完全變現＝新增 GW 的每 GW 營收等於當年基準每 VR 等值 GW 營收淨額（工作單）</t>
+          <t>Funding 第十節</t>
         </is>
       </c>
     </row>
@@ -1534,35 +1500,35 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>每 VR 等值 GW 差額（含股權報酬；追加情境：完全變現）</t>
+          <t>追加營收（完全變現）＝變現比例 × 追加 VR 等值 GW × 當年基準每 VR 等值 GW 營收淨額</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>$B/GW/年</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>-139.267405501682</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>-5.36501172129409</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>-4.82838767297759</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>-2.36820322078252</v>
+          <t>$B</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>6.19122130616515</v>
+        <v>24.4248133383653</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>12.7140716723422</v>
+        <v>93.290958584414</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>＝（基準差額 ＋ 追加營收 − 追加實付）÷（基準＋追加 VR 等值 GW）</t>
+          <t>完全變現＝新增 GW 的每 GW 營收等於當年基準每 VR 等值 GW 營收淨額（工作單）</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1545,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>差：追加情境（完全變現）− 基準（每 VR 等值 GW 差額）</t>
+          <t>每 VR 等值 GW 差額（含股權報酬；追加情境：完全變現）</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1587,25 +1553,29 @@
           <t>$B/GW/年</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>0</v>
+      <c r="E26" s="3" t="n">
+        <v>-139.267405501682</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>-5.36501172129409</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>-4.91025301987502</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>-2.69802276504026</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.284009436903216</v>
+        <v>5.74514556786612</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.580915913973501</v>
-      </c>
-      <c r="K26" s="2" t="n"/>
+        <v>12.3687697241925</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>＝（基準差額 ＋ 追加營收 − 追加實付）÷（基準＋追加 VR 等值 GW）</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1620,37 +1590,33 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>覆蓋率（追加情境：完全變現）</t>
+          <t>差：追加情境（完全變現）− 基準（每 VR 等值 GW 差額）</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>倍</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>0.345475241889585</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>0.888124307888594</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>0.773801380995813</v>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v>0.867395652649717</v>
+          <t>$B/GW/年</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1.44540734072513</v>
+        <v>0.366175640595597</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.95510635209028</v>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>營收淨額 ÷ 全成本（含股權報酬）</t>
-        </is>
-      </c>
+        <v>0.766852303386195</v>
+      </c>
+      <c r="K27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1665,52 +1631,52 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>自由現金流（追加情境：完全變現）</t>
+          <t>覆蓋率（追加情境：完全變現）</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>$B</t>
+          <t>倍</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>-6.2848</v>
+        <v>0.345475241889585</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>-2.58841935855733</v>
+        <v>0.888124307888594</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>-18.1263531954611</v>
+        <v>0.770845036748019</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>-12.5251055055554</v>
+        <v>0.851667231837521</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>61.1337135523189</v>
+        <v>1.40046437667801</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>148.358141086342</v>
+        <v>1.90567361836515</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Funding 第十節</t>
+          <t>營收淨額 ÷ 全成本（含股權報酬）</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Funding</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>F104</t>
+          <t>K281</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>第 1 層起算現金（Inputs：1＝計入 2025 年底現金；基準 0＝純營運現金流）</t>
+          <t>自由現金流（追加情境：完全變現）</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1718,17 +1684,27 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="2" t="n"/>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="n"/>
-      <c r="J29" s="2" t="n"/>
+      <c r="E29" s="3" t="n">
+        <v>-6.2848</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>-2.58841935855733</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>-18.5037194506051</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>-14.9597931224653</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>57.4352337338487</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>146.407659502562</v>
+      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2025 年底現金是過去融資所得 → 第 1 層預設不計</t>
+          <t>Funding 第十節</t>
         </is>
       </c>
     </row>
@@ -1740,12 +1716,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>F105</t>
+          <t>F104</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>自由現金流累計（2026 起）</t>
+          <t>第 1 層起算現金（Inputs：1＝計入 2025 年底現金；基準 0＝純營運現金流）</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1753,25 +1729,17 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="3" t="n">
-        <v>-2.58841935855733</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>-20.7147725540184</v>
-      </c>
-      <c r="H30" s="3" t="n">
-        <v>-33.2398780595738</v>
-      </c>
-      <c r="I30" s="3" t="n">
-        <v>18.4734380254485</v>
-      </c>
-      <c r="J30" s="3" t="n">
-        <v>118.71954056515</v>
-      </c>
+      <c r="E30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>營運現金流本身的累計；轉正前的累計負值＝需靠外部提供的資金</t>
+          <t>2025 年底現金是過去融資所得 → 第 1 層預設不計</t>
         </is>
       </c>
     </row>
@@ -1783,30 +1751,40 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>F106</t>
+          <t>F105</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>自由現金流轉正年標示（基準）</t>
+          <t>自由現金流累計（2026 起）</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>$B</t>
         </is>
       </c>
       <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="n">
-        <v>2029</v>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>2030</v>
-      </c>
-      <c r="K31" s="2" t="n"/>
+      <c r="F31" s="3" t="n">
+        <v>-2.58841935855733</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>-21.0921388091624</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>-36.0519319316277</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>11.546741429863</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>107.678201246033</v>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>營運現金流本身的累計；轉正前的累計負值＝需靠外部提供的資金</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1816,12 +1794,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>F107</t>
+          <t>F106</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>營運自由現金流首次轉正年（基準；無則「無」）</t>
+          <t>自由現金流轉正年標示（基準）</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1829,19 +1807,17 @@
           <t>年</t>
         </is>
       </c>
-      <c r="E32" s="2" t="n">
-        <v>2029</v>
-      </c>
+      <c r="E32" s="2" t="n"/>
       <c r="F32" s="2" t="n"/>
       <c r="G32" s="2" t="n"/>
       <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>第一個自給年；不代表其後每年皆為正</t>
-        </is>
-      </c>
+      <c r="I32" s="2" t="n">
+        <v>2029</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>2030</v>
+      </c>
+      <c r="K32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1851,36 +1827,32 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>F108</t>
+          <t>F107</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>補足前年底現金（基準：①營運自給（無任何融資））</t>
+          <t>營運自由現金流首次轉正年（基準；無則「無」）</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>$B</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="n"/>
-      <c r="F33" s="3" t="n">
-        <v>-2.58841935855733</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>-14.1496268340611</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>-7.60987172286504</v>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>57.5354105006191</v>
-      </c>
-      <c r="J33" s="3" t="n">
-        <v>157.781513040321</v>
-      </c>
-      <c r="K33" s="2" t="n"/>
+          <t>年</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>2029</v>
+      </c>
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="2" t="n"/>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>第一個自給年；不代表其後每年皆為正</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1890,12 +1862,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>F109</t>
+          <t>F108</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>當年外部資金需求（基準：①營運自給（無任何融資））</t>
+          <t>補足前年底現金（基準：①營運自給（無任何融資））</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1905,19 +1877,19 @@
       </c>
       <c r="E34" s="2" t="n"/>
       <c r="F34" s="3" t="n">
-        <v>6.56514571995733</v>
+        <v>-2.58841935855733</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>19.0648606167515</v>
+        <v>-14.5269930892051</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>13.4319661384618</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="2" t="n">
-        <v>0</v>
+        <v>-10.0445593397749</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>53.4207677770875</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>149.552227593258</v>
       </c>
       <c r="K34" s="2" t="n"/>
     </row>
@@ -1929,12 +1901,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>F110</t>
+          <t>F109</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>年底現金（基準：①營運自給（無任何融資））</t>
+          <t>當年外部資金需求（基準：①營運自給（無任何融資））</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1942,23 +1914,21 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E35" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E35" s="2" t="n"/>
       <c r="F35" s="3" t="n">
-        <v>3.9767263614</v>
+        <v>6.56514571995733</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>4.9152337826904</v>
+        <v>19.4422268718955</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>5.82209441559678</v>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>57.5354105006191</v>
-      </c>
-      <c r="J35" s="3" t="n">
-        <v>157.781513040321</v>
+        <v>15.8666537553716</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="K35" s="2" t="n"/>
     </row>
@@ -1970,12 +1940,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>F111</t>
+          <t>F110</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>累計外部資金需求（基準：①營運自給（無任何融資））</t>
+          <t>年底現金（基準：①營運自給（無任何融資））</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1983,21 +1953,23 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E36" s="2" t="n"/>
+      <c r="E36" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="F36" s="3" t="n">
-        <v>6.56514571995733</v>
+        <v>3.9767263614</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>25.6300063367088</v>
+        <v>4.9152337826904</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>39.0619724751706</v>
+        <v>5.82209441559678</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>39.0619724751706</v>
+        <v>53.4207677770875</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>39.0619724751706</v>
+        <v>149.552227593258</v>
       </c>
       <c r="K36" s="2" t="n"/>
     </row>
@@ -2009,12 +1981,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>F112</t>
+          <t>F111</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>補足前現金路徑（不補外部資金；基準：①營運自給（無任何融資））</t>
+          <t>累計外部資金需求（基準：①營運自給（無任何融資））</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2024,25 +1996,21 @@
       </c>
       <c r="E37" s="2" t="n"/>
       <c r="F37" s="3" t="n">
-        <v>-2.58841935855733</v>
+        <v>6.56514571995733</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>-20.7147725540184</v>
+        <v>26.0073725918528</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>-33.2398780595738</v>
+        <v>41.8740263472245</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>18.4734380254485</v>
+        <v>41.8740263472245</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>118.71954056515</v>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>可為負；谷底＝最小值</t>
-        </is>
-      </c>
+        <v>41.8740263472245</v>
+      </c>
+      <c r="K37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2052,32 +2020,40 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>F113</t>
+          <t>F112</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>缺口年標示（基準：①營運自給（無任何融資））</t>
+          <t>補足前現金路徑（不補外部資金；基準：①營運自給（無任何融資））</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>$B</t>
         </is>
       </c>
       <c r="E38" s="2" t="n"/>
-      <c r="F38" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>2027</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>2028</v>
-      </c>
-      <c r="I38" s="2" t="n"/>
-      <c r="J38" s="2" t="n"/>
-      <c r="K38" s="2" t="n"/>
+      <c r="F38" s="3" t="n">
+        <v>-2.58841935855733</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>-21.0921388091624</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>-36.0519319316277</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>11.546741429863</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>107.678201246033</v>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>可為負；谷底＝最小值</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2087,12 +2063,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>F114</t>
+          <t>F113</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>最低現金缺口首次出現年（基準：①營運自給（無任何融資）；無則「無」）</t>
+          <t>缺口年標示（基準：①營運自給（無任何融資））</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2100,12 +2076,16 @@
           <t>年</t>
         </is>
       </c>
-      <c r="E39" s="2" t="n">
+      <c r="E39" s="2" t="n"/>
+      <c r="F39" s="2" t="n">
         <v>2026</v>
       </c>
-      <c r="F39" s="2" t="n"/>
-      <c r="G39" s="2" t="n"/>
-      <c r="H39" s="2" t="n"/>
+      <c r="G39" s="2" t="n">
+        <v>2027</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>2028</v>
+      </c>
       <c r="I39" s="2" t="n"/>
       <c r="J39" s="2" t="n"/>
       <c r="K39" s="2" t="n"/>
@@ -2118,21 +2098,21 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>F115</t>
+          <t>F114</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>累計外部資金需求（基準：①營運自給（無任何融資）；2026–2030）</t>
+          <t>最低現金缺口首次出現年（基準：①營運自給（無任何融資）；無則「無」）</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>$B</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>39.0619724751706</v>
+          <t>年</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>2026</v>
       </c>
       <c r="F40" s="2" t="n"/>
       <c r="G40" s="2" t="n"/>
@@ -2149,12 +2129,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>F116</t>
+          <t>F115</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>現金谷底（基準：①營運自給（無任何融資）；補足前路徑 2026–2030 最小值）</t>
+          <t>累計外部資金需求（基準：①營運自給（無任何融資）；2026–2030）</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2163,18 +2143,14 @@
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>-33.2398780595738</v>
+        <v>41.8740263472245</v>
       </c>
       <c r="F41" s="2" t="n"/>
       <c r="G41" s="2" t="n"/>
       <c r="H41" s="2" t="n"/>
       <c r="I41" s="2" t="n"/>
       <c r="J41" s="2" t="n"/>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>負＝需外部補足的金額（不含最低現金）</t>
-        </is>
-      </c>
+      <c r="K41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2184,12 +2160,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>F117</t>
+          <t>F116</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>股權流入（基準：②加已到位股權（基準））</t>
+          <t>現金谷底（基準：①營運自給（無任何融資）；補足前路徑 2026–2030 最小值）</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2197,23 +2173,19 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E42" s="2" t="n"/>
-      <c r="F42" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="2" t="n"/>
+      <c r="E42" s="3" t="n">
+        <v>-36.0519319316277</v>
+      </c>
+      <c r="F42" s="2" t="n"/>
+      <c r="G42" s="2" t="n"/>
+      <c r="H42" s="2" t="n"/>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="2" t="n"/>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>負＝需外部補足的金額（不含最低現金）</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2223,12 +2195,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>F118</t>
+          <t>F117</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>補足前年底現金（基準：②加已到位股權（基準））</t>
+          <t>股權流入（基準：②加已到位股權（基準））</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2237,20 +2209,20 @@
         </is>
       </c>
       <c r="E43" s="2" t="n"/>
-      <c r="F43" s="3" t="n">
-        <v>117.691580641443</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>99.56522744598161</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>87.0401219404262</v>
-      </c>
-      <c r="I43" s="3" t="n">
-        <v>138.753438025449</v>
-      </c>
-      <c r="J43" s="3" t="n">
-        <v>238.99954056515</v>
+      <c r="F43" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="K43" s="2" t="n"/>
     </row>
@@ -2262,12 +2234,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>F119</t>
+          <t>F118</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>當年外部資金需求（基準：②加已到位股權（基準））</t>
+          <t>補足前年底現金（基準：②加已到位股權（基準））</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2276,20 +2248,20 @@
         </is>
       </c>
       <c r="E44" s="2" t="n"/>
-      <c r="F44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="2" t="n">
-        <v>0</v>
+      <c r="F44" s="3" t="n">
+        <v>117.691580641443</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>99.18786119083759</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>84.22806806837229</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>131.826741429863</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>227.958201246033</v>
       </c>
       <c r="K44" s="2" t="n"/>
     </row>
@@ -2301,12 +2273,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>F120</t>
+          <t>F119</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>年底現金（基準：②加已到位股權（基準））</t>
+          <t>當年外部資金需求（基準：②加已到位股權（基準））</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2314,23 +2286,21 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E45" s="3" t="n">
-        <v>20.28</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>117.691580641443</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>99.56522744598161</v>
-      </c>
-      <c r="H45" s="3" t="n">
-        <v>87.0401219404262</v>
-      </c>
-      <c r="I45" s="3" t="n">
-        <v>138.753438025449</v>
-      </c>
-      <c r="J45" s="3" t="n">
-        <v>238.99954056515</v>
+      <c r="E45" s="2" t="n"/>
+      <c r="F45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="K45" s="2" t="n"/>
     </row>
@@ -2342,12 +2312,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>F121</t>
+          <t>F120</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>累計外部資金需求（基準：②加已到位股權（基準））</t>
+          <t>年底現金（基準：②加已到位股權（基準））</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2355,21 +2325,23 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E46" s="2" t="n"/>
-      <c r="F46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="2" t="n">
-        <v>0</v>
+      <c r="E46" s="3" t="n">
+        <v>20.28</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>117.691580641443</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>99.18786119083759</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>84.22806806837229</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>131.826741429863</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>227.958201246033</v>
       </c>
       <c r="K46" s="2" t="n"/>
     </row>
@@ -2381,12 +2353,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>F122</t>
+          <t>F121</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>補足前現金路徑（不補外部資金；基準：②加已到位股權（基準））</t>
+          <t>累計外部資金需求（基準：②加已到位股權（基準））</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2395,26 +2367,22 @@
         </is>
       </c>
       <c r="E47" s="2" t="n"/>
-      <c r="F47" s="3" t="n">
-        <v>117.691580641443</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>99.56522744598161</v>
-      </c>
-      <c r="H47" s="3" t="n">
-        <v>87.0401219404262</v>
-      </c>
-      <c r="I47" s="3" t="n">
-        <v>138.753438025449</v>
-      </c>
-      <c r="J47" s="3" t="n">
-        <v>238.99954056515</v>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>可為負；谷底＝最小值</t>
-        </is>
-      </c>
+      <c r="F47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2424,26 +2392,40 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>F123</t>
+          <t>F122</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>缺口年標示（基準：②加已到位股權（基準））</t>
+          <t>補足前現金路徑（不補外部資金；基準：②加已到位股權（基準））</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>$B</t>
         </is>
       </c>
       <c r="E48" s="2" t="n"/>
-      <c r="F48" s="2" t="n"/>
-      <c r="G48" s="2" t="n"/>
-      <c r="H48" s="2" t="n"/>
-      <c r="I48" s="2" t="n"/>
-      <c r="J48" s="2" t="n"/>
-      <c r="K48" s="2" t="n"/>
+      <c r="F48" s="3" t="n">
+        <v>117.691580641443</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>99.18786119083759</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>84.22806806837229</v>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>131.826741429863</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>227.958201246033</v>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>可為負；谷底＝最小值</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2453,12 +2435,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>F124</t>
+          <t>F123</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>最低現金缺口首次出現年（基準：②加已到位股權（基準）；無則「無」）</t>
+          <t>缺口年標示（基準：②加已到位股權（基準））</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2466,11 +2448,7 @@
           <t>年</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>無</t>
-        </is>
-      </c>
+      <c r="E49" s="2" t="n"/>
       <c r="F49" s="2" t="n"/>
       <c r="G49" s="2" t="n"/>
       <c r="H49" s="2" t="n"/>
@@ -2486,21 +2464,23 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>F125</t>
+          <t>F124</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>累計外部資金需求（基準：②加已到位股權（基準）；2026–2030）</t>
+          <t>最低現金缺口首次出現年（基準：②加已到位股權（基準）；無則「無」）</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>$B</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v>0</v>
+          <t>年</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
       </c>
       <c r="F50" s="2" t="n"/>
       <c r="G50" s="2" t="n"/>
@@ -2517,12 +2497,12 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>F126</t>
+          <t>F125</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>現金谷底（基準：②加已到位股權（基準）；補足前路徑 2026–2030 最小值）</t>
+          <t>累計外部資金需求（基準：②加已到位股權（基準）；2026–2030）</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2530,19 +2510,15 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E51" s="3" t="n">
-        <v>87.0401219404262</v>
+      <c r="E51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F51" s="2" t="n"/>
       <c r="G51" s="2" t="n"/>
       <c r="H51" s="2" t="n"/>
       <c r="I51" s="2" t="n"/>
       <c r="J51" s="2" t="n"/>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>負＝需外部補足的金額（不含最低現金）</t>
-        </is>
-      </c>
+      <c r="K51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2552,12 +2528,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>F127</t>
+          <t>F126</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>股權流入（基準：③再加條件式與談判中）</t>
+          <t>現金谷底（基準：②加已到位股權（基準）；補足前路徑 2026–2030 最小值）</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2565,23 +2541,19 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E52" s="2" t="n"/>
-      <c r="F52" s="2" t="n">
-        <v>210</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="2" t="n"/>
+      <c r="E52" s="3" t="n">
+        <v>84.22806806837229</v>
+      </c>
+      <c r="F52" s="2" t="n"/>
+      <c r="G52" s="2" t="n"/>
+      <c r="H52" s="2" t="n"/>
+      <c r="I52" s="2" t="n"/>
+      <c r="J52" s="2" t="n"/>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>負＝需外部補足的金額（不含最低現金）</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2591,12 +2563,12 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>F128</t>
+          <t>F127</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>補足前年底現金（基準：③再加條件式與談判中）</t>
+          <t>股權流入（基準：③再加條件式與談判中）</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -2605,20 +2577,20 @@
         </is>
       </c>
       <c r="E53" s="2" t="n"/>
-      <c r="F53" s="3" t="n">
-        <v>227.691580641443</v>
-      </c>
-      <c r="G53" s="3" t="n">
-        <v>259.565227445982</v>
-      </c>
-      <c r="H53" s="3" t="n">
-        <v>247.040121940426</v>
-      </c>
-      <c r="I53" s="3" t="n">
-        <v>298.753438025449</v>
-      </c>
-      <c r="J53" s="3" t="n">
-        <v>398.99954056515</v>
+      <c r="F53" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="K53" s="2" t="n"/>
     </row>
@@ -2630,12 +2602,12 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>F129</t>
+          <t>F128</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>當年外部資金需求（基準：③再加條件式與談判中）</t>
+          <t>補足前年底現金（基準：③再加條件式與談判中）</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2644,20 +2616,20 @@
         </is>
       </c>
       <c r="E54" s="2" t="n"/>
-      <c r="F54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="2" t="n">
-        <v>0</v>
+      <c r="F54" s="3" t="n">
+        <v>227.691580641443</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>259.187861190838</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>244.228068068372</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>291.826741429863</v>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>387.958201246033</v>
       </c>
       <c r="K54" s="2" t="n"/>
     </row>
@@ -2669,12 +2641,12 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>F130</t>
+          <t>F129</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>年底現金（基準：③再加條件式與談判中）</t>
+          <t>當年外部資金需求（基準：③再加條件式與談判中）</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -2682,23 +2654,21 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E55" s="3" t="n">
-        <v>20.28</v>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>227.691580641443</v>
-      </c>
-      <c r="G55" s="3" t="n">
-        <v>259.565227445982</v>
-      </c>
-      <c r="H55" s="3" t="n">
-        <v>247.040121940426</v>
-      </c>
-      <c r="I55" s="3" t="n">
-        <v>298.753438025449</v>
-      </c>
-      <c r="J55" s="3" t="n">
-        <v>398.99954056515</v>
+      <c r="E55" s="2" t="n"/>
+      <c r="F55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="K55" s="2" t="n"/>
     </row>
@@ -2710,12 +2680,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>F131</t>
+          <t>F130</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>累計外部資金需求（基準：③再加條件式與談判中）</t>
+          <t>年底現金（基準：③再加條件式與談判中）</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2723,21 +2693,23 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E56" s="2" t="n"/>
-      <c r="F56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="2" t="n">
-        <v>0</v>
+      <c r="E56" s="3" t="n">
+        <v>20.28</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>227.691580641443</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>259.187861190838</v>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>244.228068068372</v>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>291.826741429863</v>
+      </c>
+      <c r="J56" s="3" t="n">
+        <v>387.958201246033</v>
       </c>
       <c r="K56" s="2" t="n"/>
     </row>
@@ -2749,12 +2721,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>F132</t>
+          <t>F131</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>補足前現金路徑（不補外部資金；基準：③再加條件式與談判中）</t>
+          <t>累計外部資金需求（基準：③再加條件式與談判中）</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2763,26 +2735,22 @@
         </is>
       </c>
       <c r="E57" s="2" t="n"/>
-      <c r="F57" s="3" t="n">
-        <v>227.691580641443</v>
-      </c>
-      <c r="G57" s="3" t="n">
-        <v>259.565227445982</v>
-      </c>
-      <c r="H57" s="3" t="n">
-        <v>247.040121940426</v>
-      </c>
-      <c r="I57" s="3" t="n">
-        <v>298.753438025449</v>
-      </c>
-      <c r="J57" s="3" t="n">
-        <v>398.99954056515</v>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>可為負；谷底＝最小值</t>
-        </is>
-      </c>
+      <c r="F57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2792,26 +2760,40 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>F133</t>
+          <t>F132</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>缺口年標示（基準：③再加條件式與談判中）</t>
+          <t>補足前現金路徑（不補外部資金；基準：③再加條件式與談判中）</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>$B</t>
         </is>
       </c>
       <c r="E58" s="2" t="n"/>
-      <c r="F58" s="2" t="n"/>
-      <c r="G58" s="2" t="n"/>
-      <c r="H58" s="2" t="n"/>
-      <c r="I58" s="2" t="n"/>
-      <c r="J58" s="2" t="n"/>
-      <c r="K58" s="2" t="n"/>
+      <c r="F58" s="3" t="n">
+        <v>227.691580641443</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>259.187861190838</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>244.228068068372</v>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>291.826741429863</v>
+      </c>
+      <c r="J58" s="3" t="n">
+        <v>387.958201246033</v>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>可為負；谷底＝最小值</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2821,12 +2803,12 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>F134</t>
+          <t>F133</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>最低現金缺口首次出現年（基準：③再加條件式與談判中；無則「無」）</t>
+          <t>缺口年標示（基準：③再加條件式與談判中）</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -2834,11 +2816,7 @@
           <t>年</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>無</t>
-        </is>
-      </c>
+      <c r="E59" s="2" t="n"/>
       <c r="F59" s="2" t="n"/>
       <c r="G59" s="2" t="n"/>
       <c r="H59" s="2" t="n"/>
@@ -2854,21 +2832,23 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>F135</t>
+          <t>F134</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>累計外部資金需求（基準：③再加條件式與談判中；2026–2030）</t>
+          <t>最低現金缺口首次出現年（基準：③再加條件式與談判中；無則「無」）</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>$B</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="n">
-        <v>0</v>
+          <t>年</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
       </c>
       <c r="F60" s="2" t="n"/>
       <c r="G60" s="2" t="n"/>
@@ -2885,12 +2865,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>F136</t>
+          <t>F135</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>現金谷底（基準：③再加條件式與談判中；補足前路徑 2026–2030 最小值）</t>
+          <t>累計外部資金需求（基準：③再加條件式與談判中；2026–2030）</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -2898,19 +2878,15 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E61" s="3" t="n">
-        <v>227.691580641443</v>
+      <c r="E61" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F61" s="2" t="n"/>
       <c r="G61" s="2" t="n"/>
       <c r="H61" s="2" t="n"/>
       <c r="I61" s="2" t="n"/>
       <c r="J61" s="2" t="n"/>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>負＝需外部補足的金額（不含最低現金）</t>
-        </is>
-      </c>
+      <c r="K61" s="2" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2920,30 +2896,32 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>F137</t>
+          <t>F136</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>自由現金流轉正年標示（擴張・無需求）</t>
+          <t>現金谷底（基準：③再加條件式與談判中；補足前路徑 2026–2030 最小值）</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>年</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="n"/>
+          <t>$B</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>227.691580641443</v>
+      </c>
       <c r="F62" s="2" t="n"/>
       <c r="G62" s="2" t="n"/>
       <c r="H62" s="2" t="n"/>
-      <c r="I62" s="2" t="n">
-        <v>2029</v>
-      </c>
-      <c r="J62" s="2" t="n">
-        <v>2030</v>
-      </c>
-      <c r="K62" s="2" t="n"/>
+      <c r="I62" s="2" t="n"/>
+      <c r="J62" s="2" t="n"/>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>負＝需外部補足的金額（不含最低現金）</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2953,12 +2931,12 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>F138</t>
+          <t>F137</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>營運自由現金流首次轉正年（擴張・無需求；無則「無」）</t>
+          <t>自由現金流轉正年標示（擴張・無需求）</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -2966,19 +2944,17 @@
           <t>年</t>
         </is>
       </c>
-      <c r="E63" s="2" t="n">
-        <v>2029</v>
-      </c>
+      <c r="E63" s="2" t="n"/>
       <c r="F63" s="2" t="n"/>
       <c r="G63" s="2" t="n"/>
       <c r="H63" s="2" t="n"/>
-      <c r="I63" s="2" t="n"/>
-      <c r="J63" s="2" t="n"/>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>第一個自給年；不代表其後每年皆為正</t>
-        </is>
-      </c>
+      <c r="I63" s="2" t="n">
+        <v>2029</v>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>2030</v>
+      </c>
+      <c r="K63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2988,36 +2964,32 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>F139</t>
+          <t>F138</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>補足前年底現金（擴張・無需求：①營運自給（無任何融資））</t>
+          <t>營運自由現金流首次轉正年（擴張・無需求；無則「無」）</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>$B</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="n"/>
-      <c r="F64" s="3" t="n">
-        <v>-2.58841935855733</v>
-      </c>
-      <c r="G64" s="3" t="n">
-        <v>-14.1496268340611</v>
-      </c>
-      <c r="H64" s="3" t="n">
-        <v>-7.60987172286505</v>
-      </c>
-      <c r="I64" s="3" t="n">
-        <v>43.5643539431415</v>
-      </c>
-      <c r="J64" s="3" t="n">
-        <v>102.64728681041</v>
-      </c>
-      <c r="K64" s="2" t="n"/>
+          <t>年</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>2029</v>
+      </c>
+      <c r="F64" s="2" t="n"/>
+      <c r="G64" s="2" t="n"/>
+      <c r="H64" s="2" t="n"/>
+      <c r="I64" s="2" t="n"/>
+      <c r="J64" s="2" t="n"/>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>第一個自給年；不代表其後每年皆為正</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3027,12 +2999,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>F140</t>
+          <t>F139</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>當年外部資金需求（擴張・無需求：①營運自給（無任何融資））</t>
+          <t>補足前年底現金（擴張・無需求：①營運自給（無任何融資））</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3042,19 +3014,19 @@
       </c>
       <c r="E65" s="2" t="n"/>
       <c r="F65" s="3" t="n">
-        <v>6.56514571995733</v>
+        <v>-2.58841935855733</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>19.0648606167515</v>
+        <v>-14.5269930892051</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>13.4319661384618</v>
-      </c>
-      <c r="I65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="2" t="n">
-        <v>0</v>
+        <v>-10.0445593397749</v>
+      </c>
+      <c r="I65" s="3" t="n">
+        <v>38.8325148110802</v>
+      </c>
+      <c r="J65" s="3" t="n">
+        <v>91.9492157292283</v>
       </c>
       <c r="K65" s="2" t="n"/>
     </row>
@@ -3066,12 +3038,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>F141</t>
+          <t>F140</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>年底現金（擴張・無需求：①營運自給（無任何融資））</t>
+          <t>當年外部資金需求（擴張・無需求：①營運自給（無任何融資））</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3079,23 +3051,21 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E66" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E66" s="2" t="n"/>
       <c r="F66" s="3" t="n">
-        <v>3.9767263614</v>
+        <v>6.56514571995733</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>4.9152337826904</v>
+        <v>19.4422268718955</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>5.82209441559678</v>
-      </c>
-      <c r="I66" s="3" t="n">
-        <v>43.5643539431415</v>
-      </c>
-      <c r="J66" s="3" t="n">
-        <v>102.64728681041</v>
+        <v>15.8666537553717</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="K66" s="2" t="n"/>
     </row>
@@ -3107,12 +3077,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>F142</t>
+          <t>F141</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>累計外部資金需求（擴張・無需求：①營運自給（無任何融資））</t>
+          <t>年底現金（擴張・無需求：①營運自給（無任何融資））</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3120,21 +3090,23 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E67" s="2" t="n"/>
+      <c r="E67" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="F67" s="3" t="n">
-        <v>6.56514571995733</v>
+        <v>3.9767263614</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>25.6300063367088</v>
+        <v>4.9152337826904</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>39.0619724751706</v>
+        <v>5.82209441559678</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>39.0619724751706</v>
+        <v>38.8325148110802</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>39.0619724751706</v>
+        <v>91.9492157292283</v>
       </c>
       <c r="K67" s="2" t="n"/>
     </row>
@@ -3146,12 +3118,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>F143</t>
+          <t>F142</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>補足前現金路徑（不補外部資金；擴張・無需求：①營運自給（無任何融資））</t>
+          <t>累計外部資金需求（擴張・無需求：①營運自給（無任何融資））</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3161,25 +3133,21 @@
       </c>
       <c r="E68" s="2" t="n"/>
       <c r="F68" s="3" t="n">
-        <v>-2.58841935855733</v>
+        <v>6.56514571995733</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>-20.7147725540184</v>
+        <v>26.0073725918528</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>-33.2398780595738</v>
+        <v>41.8740263472245</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>4.5023814679709</v>
+        <v>41.8740263472245</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>63.5853143352398</v>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>可為負；谷底＝最小值</t>
-        </is>
-      </c>
+        <v>41.8740263472245</v>
+      </c>
+      <c r="K68" s="2" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -3189,32 +3157,40 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>F144</t>
+          <t>F143</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>缺口年標示（擴張・無需求：①營運自給（無任何融資））</t>
+          <t>補足前現金路徑（不補外部資金；擴張・無需求：①營運自給（無任何融資））</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>$B</t>
         </is>
       </c>
       <c r="E69" s="2" t="n"/>
-      <c r="F69" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G69" s="2" t="n">
-        <v>2027</v>
-      </c>
-      <c r="H69" s="2" t="n">
-        <v>2028</v>
-      </c>
-      <c r="I69" s="2" t="n"/>
-      <c r="J69" s="2" t="n"/>
-      <c r="K69" s="2" t="n"/>
+      <c r="F69" s="3" t="n">
+        <v>-2.58841935855733</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>-21.0921388091624</v>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>-36.0519319316277</v>
+      </c>
+      <c r="I69" s="3" t="n">
+        <v>-3.04151153614433</v>
+      </c>
+      <c r="J69" s="3" t="n">
+        <v>50.0751893820038</v>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>可為負；谷底＝最小值</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -3224,12 +3200,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>F145</t>
+          <t>F144</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>最低現金缺口首次出現年（擴張・無需求：①營運自給（無任何融資）；無則「無」）</t>
+          <t>缺口年標示（擴張・無需求：①營運自給（無任何融資））</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3237,12 +3213,16 @@
           <t>年</t>
         </is>
       </c>
-      <c r="E70" s="2" t="n">
+      <c r="E70" s="2" t="n"/>
+      <c r="F70" s="2" t="n">
         <v>2026</v>
       </c>
-      <c r="F70" s="2" t="n"/>
-      <c r="G70" s="2" t="n"/>
-      <c r="H70" s="2" t="n"/>
+      <c r="G70" s="2" t="n">
+        <v>2027</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>2028</v>
+      </c>
       <c r="I70" s="2" t="n"/>
       <c r="J70" s="2" t="n"/>
       <c r="K70" s="2" t="n"/>
@@ -3255,21 +3235,21 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>F146</t>
+          <t>F145</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>累計外部資金需求（擴張・無需求：①營運自給（無任何融資）；2026–2030）</t>
+          <t>最低現金缺口首次出現年（擴張・無需求：①營運自給（無任何融資）；無則「無」）</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>$B</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="n">
-        <v>39.0619724751706</v>
+          <t>年</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>2026</v>
       </c>
       <c r="F71" s="2" t="n"/>
       <c r="G71" s="2" t="n"/>
@@ -3286,12 +3266,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>F147</t>
+          <t>F146</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>現金谷底（擴張・無需求：①營運自給（無任何融資）；補足前路徑 2026–2030 最小值）</t>
+          <t>累計外部資金需求（擴張・無需求：①營運自給（無任何融資）；2026–2030）</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3300,18 +3280,14 @@
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>-33.2398780595738</v>
+        <v>41.8740263472245</v>
       </c>
       <c r="F72" s="2" t="n"/>
       <c r="G72" s="2" t="n"/>
       <c r="H72" s="2" t="n"/>
       <c r="I72" s="2" t="n"/>
       <c r="J72" s="2" t="n"/>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>負＝需外部補足的金額（不含最低現金）</t>
-        </is>
-      </c>
+      <c r="K72" s="2" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -3321,12 +3297,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>F148</t>
+          <t>F147</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>股權流入（擴張・無需求：②加已到位股權（基準））</t>
+          <t>現金谷底（擴張・無需求：①營運自給（無任何融資）；補足前路徑 2026–2030 最小值）</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3334,23 +3310,19 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E73" s="2" t="n"/>
-      <c r="F73" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="G73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" s="2" t="n"/>
+      <c r="E73" s="3" t="n">
+        <v>-36.0519319316277</v>
+      </c>
+      <c r="F73" s="2" t="n"/>
+      <c r="G73" s="2" t="n"/>
+      <c r="H73" s="2" t="n"/>
+      <c r="I73" s="2" t="n"/>
+      <c r="J73" s="2" t="n"/>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>負＝需外部補足的金額（不含最低現金）</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -3360,12 +3332,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>F149</t>
+          <t>F148</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>補足前年底現金（擴張・無需求：②加已到位股權（基準））</t>
+          <t>股權流入（擴張・無需求：②加已到位股權（基準））</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3374,20 +3346,20 @@
         </is>
       </c>
       <c r="E74" s="2" t="n"/>
-      <c r="F74" s="3" t="n">
-        <v>117.691580641443</v>
-      </c>
-      <c r="G74" s="3" t="n">
-        <v>99.56522744598161</v>
-      </c>
-      <c r="H74" s="3" t="n">
-        <v>87.0401219404262</v>
-      </c>
-      <c r="I74" s="3" t="n">
-        <v>124.782381467971</v>
-      </c>
-      <c r="J74" s="3" t="n">
-        <v>183.86531433524</v>
+      <c r="F74" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="K74" s="2" t="n"/>
     </row>
@@ -3399,12 +3371,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>F150</t>
+          <t>F149</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>當年外部資金需求（擴張・無需求：②加已到位股權（基準））</t>
+          <t>補足前年底現金（擴張・無需求：②加已到位股權（基準））</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3413,20 +3385,20 @@
         </is>
       </c>
       <c r="E75" s="2" t="n"/>
-      <c r="F75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="2" t="n">
-        <v>0</v>
+      <c r="F75" s="3" t="n">
+        <v>117.691580641443</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>99.18786119083759</v>
+      </c>
+      <c r="H75" s="3" t="n">
+        <v>84.22806806837229</v>
+      </c>
+      <c r="I75" s="3" t="n">
+        <v>117.238488463856</v>
+      </c>
+      <c r="J75" s="3" t="n">
+        <v>170.355189382004</v>
       </c>
       <c r="K75" s="2" t="n"/>
     </row>
@@ -3438,12 +3410,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>F151</t>
+          <t>F150</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>年底現金（擴張・無需求：②加已到位股權（基準））</t>
+          <t>當年外部資金需求（擴張・無需求：②加已到位股權（基準））</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3451,23 +3423,21 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E76" s="3" t="n">
-        <v>20.28</v>
-      </c>
-      <c r="F76" s="3" t="n">
-        <v>117.691580641443</v>
-      </c>
-      <c r="G76" s="3" t="n">
-        <v>99.56522744598161</v>
-      </c>
-      <c r="H76" s="3" t="n">
-        <v>87.0401219404262</v>
-      </c>
-      <c r="I76" s="3" t="n">
-        <v>124.782381467971</v>
-      </c>
-      <c r="J76" s="3" t="n">
-        <v>183.86531433524</v>
+      <c r="E76" s="2" t="n"/>
+      <c r="F76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="K76" s="2" t="n"/>
     </row>
@@ -3479,12 +3449,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>F152</t>
+          <t>F151</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>累計外部資金需求（擴張・無需求：②加已到位股權（基準））</t>
+          <t>年底現金（擴張・無需求：②加已到位股權（基準））</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3492,21 +3462,23 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E77" s="2" t="n"/>
-      <c r="F77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="2" t="n">
-        <v>0</v>
+      <c r="E77" s="3" t="n">
+        <v>20.28</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>117.691580641443</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>99.18786119083759</v>
+      </c>
+      <c r="H77" s="3" t="n">
+        <v>84.22806806837229</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>117.238488463856</v>
+      </c>
+      <c r="J77" s="3" t="n">
+        <v>170.355189382004</v>
       </c>
       <c r="K77" s="2" t="n"/>
     </row>
@@ -3518,12 +3490,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>F153</t>
+          <t>F152</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>補足前現金路徑（不補外部資金；擴張・無需求：②加已到位股權（基準））</t>
+          <t>累計外部資金需求（擴張・無需求：②加已到位股權（基準））</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -3532,26 +3504,22 @@
         </is>
       </c>
       <c r="E78" s="2" t="n"/>
-      <c r="F78" s="3" t="n">
-        <v>117.691580641443</v>
-      </c>
-      <c r="G78" s="3" t="n">
-        <v>99.56522744598161</v>
-      </c>
-      <c r="H78" s="3" t="n">
-        <v>87.0401219404262</v>
-      </c>
-      <c r="I78" s="3" t="n">
-        <v>124.782381467971</v>
-      </c>
-      <c r="J78" s="3" t="n">
-        <v>183.86531433524</v>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>可為負；谷底＝最小值</t>
-        </is>
-      </c>
+      <c r="F78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -3561,26 +3529,40 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>F154</t>
+          <t>F153</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>缺口年標示（擴張・無需求：②加已到位股權（基準））</t>
+          <t>補足前現金路徑（不補外部資金；擴張・無需求：②加已到位股權（基準））</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>$B</t>
         </is>
       </c>
       <c r="E79" s="2" t="n"/>
-      <c r="F79" s="2" t="n"/>
-      <c r="G79" s="2" t="n"/>
-      <c r="H79" s="2" t="n"/>
-      <c r="I79" s="2" t="n"/>
-      <c r="J79" s="2" t="n"/>
-      <c r="K79" s="2" t="n"/>
+      <c r="F79" s="3" t="n">
+        <v>117.691580641443</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>99.18786119083759</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>84.22806806837229</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>117.238488463856</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>170.355189382004</v>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>可為負；谷底＝最小值</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -3590,12 +3572,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>F155</t>
+          <t>F154</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>最低現金缺口首次出現年（擴張・無需求：②加已到位股權（基準）；無則「無」）</t>
+          <t>缺口年標示（擴張・無需求：②加已到位股權（基準））</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -3603,11 +3585,7 @@
           <t>年</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>無</t>
-        </is>
-      </c>
+      <c r="E80" s="2" t="n"/>
       <c r="F80" s="2" t="n"/>
       <c r="G80" s="2" t="n"/>
       <c r="H80" s="2" t="n"/>
@@ -3623,21 +3601,23 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>F156</t>
+          <t>F155</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>累計外部資金需求（擴張・無需求：②加已到位股權（基準）；2026–2030）</t>
+          <t>最低現金缺口首次出現年（擴張・無需求：②加已到位股權（基準）；無則「無」）</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>$B</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="n">
-        <v>0</v>
+          <t>年</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
       </c>
       <c r="F81" s="2" t="n"/>
       <c r="G81" s="2" t="n"/>
@@ -3654,12 +3634,12 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>F157</t>
+          <t>F156</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>現金谷底（擴張・無需求：②加已到位股權（基準）；補足前路徑 2026–2030 最小值）</t>
+          <t>累計外部資金需求（擴張・無需求：②加已到位股權（基準）；2026–2030）</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -3667,19 +3647,15 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E82" s="3" t="n">
-        <v>87.0401219404262</v>
+      <c r="E82" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F82" s="2" t="n"/>
       <c r="G82" s="2" t="n"/>
       <c r="H82" s="2" t="n"/>
       <c r="I82" s="2" t="n"/>
       <c r="J82" s="2" t="n"/>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>負＝需外部補足的金額（不含最低現金）</t>
-        </is>
-      </c>
+      <c r="K82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -3689,12 +3665,12 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>F158</t>
+          <t>F157</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>股權流入（擴張・無需求：③再加條件式與談判中）</t>
+          <t>現金谷底（擴張・無需求：②加已到位股權（基準）；補足前路徑 2026–2030 最小值）</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -3702,23 +3678,19 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E83" s="2" t="n"/>
-      <c r="F83" s="2" t="n">
-        <v>210</v>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="H83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" s="2" t="n"/>
+      <c r="E83" s="3" t="n">
+        <v>84.22806806837229</v>
+      </c>
+      <c r="F83" s="2" t="n"/>
+      <c r="G83" s="2" t="n"/>
+      <c r="H83" s="2" t="n"/>
+      <c r="I83" s="2" t="n"/>
+      <c r="J83" s="2" t="n"/>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>負＝需外部補足的金額（不含最低現金）</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -3728,12 +3700,12 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>F159</t>
+          <t>F158</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>補足前年底現金（擴張・無需求：③再加條件式與談判中）</t>
+          <t>股權流入（擴張・無需求：③再加條件式與談判中）</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -3742,20 +3714,20 @@
         </is>
       </c>
       <c r="E84" s="2" t="n"/>
-      <c r="F84" s="3" t="n">
-        <v>227.691580641443</v>
-      </c>
-      <c r="G84" s="3" t="n">
-        <v>259.565227445982</v>
-      </c>
-      <c r="H84" s="3" t="n">
-        <v>247.040121940426</v>
-      </c>
-      <c r="I84" s="3" t="n">
-        <v>284.782381467971</v>
-      </c>
-      <c r="J84" s="3" t="n">
-        <v>343.86531433524</v>
+      <c r="F84" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="K84" s="2" t="n"/>
     </row>
@@ -3767,12 +3739,12 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>F160</t>
+          <t>F159</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>當年外部資金需求（擴張・無需求：③再加條件式與談判中）</t>
+          <t>補足前年底現金（擴張・無需求：③再加條件式與談判中）</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -3781,20 +3753,20 @@
         </is>
       </c>
       <c r="E85" s="2" t="n"/>
-      <c r="F85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="2" t="n">
-        <v>0</v>
+      <c r="F85" s="3" t="n">
+        <v>227.691580641443</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>259.187861190838</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>244.228068068372</v>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>277.238488463856</v>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>330.355189382004</v>
       </c>
       <c r="K85" s="2" t="n"/>
     </row>
@@ -3806,12 +3778,12 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>F161</t>
+          <t>F160</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>年底現金（擴張・無需求：③再加條件式與談判中）</t>
+          <t>當年外部資金需求（擴張・無需求：③再加條件式與談判中）</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -3819,23 +3791,21 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E86" s="3" t="n">
-        <v>20.28</v>
-      </c>
-      <c r="F86" s="3" t="n">
-        <v>227.691580641443</v>
-      </c>
-      <c r="G86" s="3" t="n">
-        <v>259.565227445982</v>
-      </c>
-      <c r="H86" s="3" t="n">
-        <v>247.040121940426</v>
-      </c>
-      <c r="I86" s="3" t="n">
-        <v>284.782381467971</v>
-      </c>
-      <c r="J86" s="3" t="n">
-        <v>343.86531433524</v>
+      <c r="E86" s="2" t="n"/>
+      <c r="F86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="K86" s="2" t="n"/>
     </row>
@@ -3847,12 +3817,12 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>F162</t>
+          <t>F161</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>累計外部資金需求（擴張・無需求：③再加條件式與談判中）</t>
+          <t>年底現金（擴張・無需求：③再加條件式與談判中）</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -3860,21 +3830,23 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E87" s="2" t="n"/>
-      <c r="F87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="2" t="n">
-        <v>0</v>
+      <c r="E87" s="3" t="n">
+        <v>20.28</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>227.691580641443</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>259.187861190838</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>244.228068068372</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>277.238488463856</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>330.355189382004</v>
       </c>
       <c r="K87" s="2" t="n"/>
     </row>
@@ -3886,12 +3858,12 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>F163</t>
+          <t>F162</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>補足前現金路徑（不補外部資金；擴張・無需求：③再加條件式與談判中）</t>
+          <t>累計外部資金需求（擴張・無需求：③再加條件式與談判中）</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -3900,26 +3872,22 @@
         </is>
       </c>
       <c r="E88" s="2" t="n"/>
-      <c r="F88" s="3" t="n">
-        <v>227.691580641443</v>
-      </c>
-      <c r="G88" s="3" t="n">
-        <v>259.565227445982</v>
-      </c>
-      <c r="H88" s="3" t="n">
-        <v>247.040121940426</v>
-      </c>
-      <c r="I88" s="3" t="n">
-        <v>284.782381467971</v>
-      </c>
-      <c r="J88" s="3" t="n">
-        <v>343.86531433524</v>
-      </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>可為負；谷底＝最小值</t>
-        </is>
-      </c>
+      <c r="F88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="2" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -3929,26 +3897,40 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>F164</t>
+          <t>F163</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>缺口年標示（擴張・無需求：③再加條件式與談判中）</t>
+          <t>補足前現金路徑（不補外部資金；擴張・無需求：③再加條件式與談判中）</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>$B</t>
         </is>
       </c>
       <c r="E89" s="2" t="n"/>
-      <c r="F89" s="2" t="n"/>
-      <c r="G89" s="2" t="n"/>
-      <c r="H89" s="2" t="n"/>
-      <c r="I89" s="2" t="n"/>
-      <c r="J89" s="2" t="n"/>
-      <c r="K89" s="2" t="n"/>
+      <c r="F89" s="3" t="n">
+        <v>227.691580641443</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>259.187861190838</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>244.228068068372</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>277.238488463856</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>330.355189382004</v>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>可為負；谷底＝最小值</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -3958,12 +3940,12 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>F165</t>
+          <t>F164</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>最低現金缺口首次出現年（擴張・無需求：③再加條件式與談判中；無則「無」）</t>
+          <t>缺口年標示（擴張・無需求：③再加條件式與談判中）</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -3971,11 +3953,7 @@
           <t>年</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>無</t>
-        </is>
-      </c>
+      <c r="E90" s="2" t="n"/>
       <c r="F90" s="2" t="n"/>
       <c r="G90" s="2" t="n"/>
       <c r="H90" s="2" t="n"/>
@@ -3991,21 +3969,23 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>F166</t>
+          <t>F165</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>累計外部資金需求（擴張・無需求：③再加條件式與談判中；2026–2030）</t>
+          <t>最低現金缺口首次出現年（擴張・無需求：③再加條件式與談判中；無則「無」）</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>$B</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="n">
-        <v>0</v>
+          <t>年</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
       </c>
       <c r="F91" s="2" t="n"/>
       <c r="G91" s="2" t="n"/>
@@ -4022,12 +4002,12 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>F167</t>
+          <t>F166</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>現金谷底（擴張・無需求：③再加條件式與談判中；補足前路徑 2026–2030 最小值）</t>
+          <t>累計外部資金需求（擴張・無需求：③再加條件式與談判中；2026–2030）</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -4035,19 +4015,15 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E92" s="3" t="n">
-        <v>227.691580641443</v>
+      <c r="E92" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F92" s="2" t="n"/>
       <c r="G92" s="2" t="n"/>
       <c r="H92" s="2" t="n"/>
       <c r="I92" s="2" t="n"/>
       <c r="J92" s="2" t="n"/>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>負＝需外部補足的金額（不含最低現金）</t>
-        </is>
-      </c>
+      <c r="K92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -4057,30 +4033,32 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>F168</t>
+          <t>F167</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>自由現金流轉正年標示（擴張・部分變現）</t>
+          <t>現金谷底（擴張・無需求：③再加條件式與談判中；補足前路徑 2026–2030 最小值）</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>年</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="n"/>
+          <t>$B</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>227.691580641443</v>
+      </c>
       <c r="F93" s="2" t="n"/>
       <c r="G93" s="2" t="n"/>
       <c r="H93" s="2" t="n"/>
-      <c r="I93" s="2" t="n">
-        <v>2029</v>
-      </c>
-      <c r="J93" s="2" t="n">
-        <v>2030</v>
-      </c>
-      <c r="K93" s="2" t="n"/>
+      <c r="I93" s="2" t="n"/>
+      <c r="J93" s="2" t="n"/>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>負＝需外部補足的金額（不含最低現金）</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -4090,12 +4068,12 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>F169</t>
+          <t>F168</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>營運自由現金流首次轉正年（擴張・部分變現；無則「無」）</t>
+          <t>自由現金流轉正年標示（擴張・部分變現）</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -4103,19 +4081,17 @@
           <t>年</t>
         </is>
       </c>
-      <c r="E94" s="2" t="n">
-        <v>2029</v>
-      </c>
+      <c r="E94" s="2" t="n"/>
       <c r="F94" s="2" t="n"/>
       <c r="G94" s="2" t="n"/>
       <c r="H94" s="2" t="n"/>
-      <c r="I94" s="2" t="n"/>
-      <c r="J94" s="2" t="n"/>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>第一個自給年；不代表其後每年皆為正</t>
-        </is>
-      </c>
+      <c r="I94" s="2" t="n">
+        <v>2029</v>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>2030</v>
+      </c>
+      <c r="K94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -4125,36 +4101,32 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>F170</t>
+          <t>F169</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>補足前年底現金（擴張・部分變現：①營運自給（無任何融資））</t>
+          <t>營運自由現金流首次轉正年（擴張・部分變現；無則「無」）</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>$B</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="n"/>
-      <c r="F95" s="3" t="n">
-        <v>-2.58841935855733</v>
-      </c>
-      <c r="G95" s="3" t="n">
-        <v>-14.1496268340611</v>
-      </c>
-      <c r="H95" s="3" t="n">
-        <v>-7.60987172286505</v>
-      </c>
-      <c r="I95" s="3" t="n">
-        <v>55.2600809555286</v>
-      </c>
-      <c r="J95" s="3" t="n">
-        <v>158.980617932334</v>
-      </c>
-      <c r="K95" s="2" t="n"/>
+          <t>年</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>2029</v>
+      </c>
+      <c r="F95" s="2" t="n"/>
+      <c r="G95" s="2" t="n"/>
+      <c r="H95" s="2" t="n"/>
+      <c r="I95" s="2" t="n"/>
+      <c r="J95" s="2" t="n"/>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>第一個自給年；不代表其後每年皆為正</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -4164,12 +4136,12 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>F171</t>
+          <t>F170</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>當年外部資金需求（擴張・部分變現：①營運自給（無任何融資））</t>
+          <t>補足前年底現金（擴張・部分變現：①營運自給（無任何融資））</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -4179,19 +4151,19 @@
       </c>
       <c r="E96" s="2" t="n"/>
       <c r="F96" s="3" t="n">
-        <v>6.56514571995733</v>
+        <v>-2.58841935855733</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>19.0648606167515</v>
+        <v>-14.5269930892051</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>13.4319661384618</v>
-      </c>
-      <c r="I96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="2" t="n">
-        <v>0</v>
+        <v>-10.0445593397749</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>51.0449214802628</v>
+      </c>
+      <c r="J96" s="3" t="n">
+        <v>150.807101690618</v>
       </c>
       <c r="K96" s="2" t="n"/>
     </row>
@@ -4203,12 +4175,12 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>F172</t>
+          <t>F171</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>年底現金（擴張・部分變現：①營運自給（無任何融資））</t>
+          <t>當年外部資金需求（擴張・部分變現：①營運自給（無任何融資））</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -4216,23 +4188,21 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E97" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E97" s="2" t="n"/>
       <c r="F97" s="3" t="n">
-        <v>3.9767263614</v>
+        <v>6.56514571995733</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>4.9152337826904</v>
+        <v>19.4422268718955</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>5.82209441559678</v>
-      </c>
-      <c r="I97" s="3" t="n">
-        <v>55.2600809555286</v>
-      </c>
-      <c r="J97" s="3" t="n">
-        <v>158.980617932334</v>
+        <v>15.8666537553717</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="K97" s="2" t="n"/>
     </row>
@@ -4244,12 +4214,12 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>F173</t>
+          <t>F172</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>累計外部資金需求（擴張・部分變現：①營運自給（無任何融資））</t>
+          <t>年底現金（擴張・部分變現：①營運自給（無任何融資））</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -4257,21 +4227,23 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E98" s="2" t="n"/>
+      <c r="E98" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="F98" s="3" t="n">
-        <v>6.56514571995733</v>
+        <v>3.9767263614</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>25.6300063367088</v>
+        <v>4.9152337826904</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>39.0619724751706</v>
+        <v>5.82209441559678</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>39.0619724751706</v>
+        <v>51.0449214802628</v>
       </c>
       <c r="J98" s="3" t="n">
-        <v>39.0619724751706</v>
+        <v>150.807101690618</v>
       </c>
       <c r="K98" s="2" t="n"/>
     </row>
@@ -4283,12 +4255,12 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>F174</t>
+          <t>F173</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>補足前現金路徑（不補外部資金；擴張・部分變現：①營運自給（無任何融資））</t>
+          <t>累計外部資金需求（擴張・部分變現：①營運自給（無任何融資））</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -4298,25 +4270,21 @@
       </c>
       <c r="E99" s="2" t="n"/>
       <c r="F99" s="3" t="n">
-        <v>-2.58841935855733</v>
+        <v>6.56514571995733</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>-20.7147725540184</v>
+        <v>26.0073725918528</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>-33.2398780595738</v>
+        <v>41.8740263472245</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>16.198108480358</v>
+        <v>41.8740263472245</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>119.918645457163</v>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>可為負；谷底＝最小值</t>
-        </is>
-      </c>
+        <v>41.8740263472245</v>
+      </c>
+      <c r="K99" s="2" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -4326,32 +4294,40 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>F175</t>
+          <t>F174</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>缺口年標示（擴張・部分變現：①營運自給（無任何融資））</t>
+          <t>補足前現金路徑（不補外部資金；擴張・部分變現：①營運自給（無任何融資））</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>$B</t>
         </is>
       </c>
       <c r="E100" s="2" t="n"/>
-      <c r="F100" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G100" s="2" t="n">
-        <v>2027</v>
-      </c>
-      <c r="H100" s="2" t="n">
-        <v>2028</v>
-      </c>
-      <c r="I100" s="2" t="n"/>
-      <c r="J100" s="2" t="n"/>
-      <c r="K100" s="2" t="n"/>
+      <c r="F100" s="3" t="n">
+        <v>-2.58841935855733</v>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>-21.0921388091624</v>
+      </c>
+      <c r="H100" s="3" t="n">
+        <v>-36.0519319316277</v>
+      </c>
+      <c r="I100" s="3" t="n">
+        <v>9.17089513303833</v>
+      </c>
+      <c r="J100" s="3" t="n">
+        <v>108.933075343393</v>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>可為負；谷底＝最小值</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -4361,12 +4337,12 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>F176</t>
+          <t>F175</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>最低現金缺口首次出現年（擴張・部分變現：①營運自給（無任何融資）；無則「無」）</t>
+          <t>缺口年標示（擴張・部分變現：①營運自給（無任何融資））</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -4374,12 +4350,16 @@
           <t>年</t>
         </is>
       </c>
-      <c r="E101" s="2" t="n">
+      <c r="E101" s="2" t="n"/>
+      <c r="F101" s="2" t="n">
         <v>2026</v>
       </c>
-      <c r="F101" s="2" t="n"/>
-      <c r="G101" s="2" t="n"/>
-      <c r="H101" s="2" t="n"/>
+      <c r="G101" s="2" t="n">
+        <v>2027</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>2028</v>
+      </c>
       <c r="I101" s="2" t="n"/>
       <c r="J101" s="2" t="n"/>
       <c r="K101" s="2" t="n"/>
@@ -4392,21 +4372,21 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>F177</t>
+          <t>F176</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>累計外部資金需求（擴張・部分變現：①營運自給（無任何融資）；2026–2030）</t>
+          <t>最低現金缺口首次出現年（擴張・部分變現：①營運自給（無任何融資）；無則「無」）</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>$B</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="n">
-        <v>39.0619724751706</v>
+          <t>年</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>2026</v>
       </c>
       <c r="F102" s="2" t="n"/>
       <c r="G102" s="2" t="n"/>
@@ -4423,12 +4403,12 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>F178</t>
+          <t>F177</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>現金谷底（擴張・部分變現：①營運自給（無任何融資）；補足前路徑 2026–2030 最小值）</t>
+          <t>累計外部資金需求（擴張・部分變現：①營運自給（無任何融資）；2026–2030）</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -4437,18 +4417,14 @@
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>-33.2398780595738</v>
+        <v>41.8740263472245</v>
       </c>
       <c r="F103" s="2" t="n"/>
       <c r="G103" s="2" t="n"/>
       <c r="H103" s="2" t="n"/>
       <c r="I103" s="2" t="n"/>
       <c r="J103" s="2" t="n"/>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>負＝需外部補足的金額（不含最低現金）</t>
-        </is>
-      </c>
+      <c r="K103" s="2" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -4458,12 +4434,12 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>F179</t>
+          <t>F178</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>股權流入（擴張・部分變現：②加已到位股權（基準））</t>
+          <t>現金谷底（擴張・部分變現：①營運自給（無任何融資）；補足前路徑 2026–2030 最小值）</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -4471,23 +4447,19 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E104" s="2" t="n"/>
-      <c r="F104" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="G104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" s="2" t="n"/>
+      <c r="E104" s="3" t="n">
+        <v>-36.0519319316277</v>
+      </c>
+      <c r="F104" s="2" t="n"/>
+      <c r="G104" s="2" t="n"/>
+      <c r="H104" s="2" t="n"/>
+      <c r="I104" s="2" t="n"/>
+      <c r="J104" s="2" t="n"/>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>負＝需外部補足的金額（不含最低現金）</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -4497,12 +4469,12 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>F180</t>
+          <t>F179</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>補足前年底現金（擴張・部分變現：②加已到位股權（基準））</t>
+          <t>股權流入（擴張・部分變現：②加已到位股權（基準））</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -4511,20 +4483,20 @@
         </is>
       </c>
       <c r="E105" s="2" t="n"/>
-      <c r="F105" s="3" t="n">
-        <v>117.691580641443</v>
-      </c>
-      <c r="G105" s="3" t="n">
-        <v>99.56522744598161</v>
-      </c>
-      <c r="H105" s="3" t="n">
-        <v>87.0401219404262</v>
-      </c>
-      <c r="I105" s="3" t="n">
-        <v>136.478108480358</v>
-      </c>
-      <c r="J105" s="3" t="n">
-        <v>240.198645457163</v>
+      <c r="F105" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="K105" s="2" t="n"/>
     </row>
@@ -4536,12 +4508,12 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>F181</t>
+          <t>F180</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>當年外部資金需求（擴張・部分變現：②加已到位股權（基準））</t>
+          <t>補足前年底現金（擴張・部分變現：②加已到位股權（基準））</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -4550,20 +4522,20 @@
         </is>
       </c>
       <c r="E106" s="2" t="n"/>
-      <c r="F106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" s="2" t="n">
-        <v>0</v>
+      <c r="F106" s="3" t="n">
+        <v>117.691580641443</v>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>99.18786119083759</v>
+      </c>
+      <c r="H106" s="3" t="n">
+        <v>84.22806806837229</v>
+      </c>
+      <c r="I106" s="3" t="n">
+        <v>129.450895133038</v>
+      </c>
+      <c r="J106" s="3" t="n">
+        <v>229.213075343393</v>
       </c>
       <c r="K106" s="2" t="n"/>
     </row>
@@ -4575,12 +4547,12 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>F182</t>
+          <t>F181</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>年底現金（擴張・部分變現：②加已到位股權（基準））</t>
+          <t>當年外部資金需求（擴張・部分變現：②加已到位股權（基準））</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -4588,23 +4560,21 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E107" s="3" t="n">
-        <v>20.28</v>
-      </c>
-      <c r="F107" s="3" t="n">
-        <v>117.691580641443</v>
-      </c>
-      <c r="G107" s="3" t="n">
-        <v>99.56522744598161</v>
-      </c>
-      <c r="H107" s="3" t="n">
-        <v>87.0401219404262</v>
-      </c>
-      <c r="I107" s="3" t="n">
-        <v>136.478108480358</v>
-      </c>
-      <c r="J107" s="3" t="n">
-        <v>240.198645457163</v>
+      <c r="E107" s="2" t="n"/>
+      <c r="F107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="K107" s="2" t="n"/>
     </row>
@@ -4616,12 +4586,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>F183</t>
+          <t>F182</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>累計外部資金需求（擴張・部分變現：②加已到位股權（基準））</t>
+          <t>年底現金（擴張・部分變現：②加已到位股權（基準））</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -4629,21 +4599,23 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E108" s="2" t="n"/>
-      <c r="F108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" s="2" t="n">
-        <v>0</v>
+      <c r="E108" s="3" t="n">
+        <v>20.28</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>117.691580641443</v>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>99.18786119083759</v>
+      </c>
+      <c r="H108" s="3" t="n">
+        <v>84.22806806837229</v>
+      </c>
+      <c r="I108" s="3" t="n">
+        <v>129.450895133038</v>
+      </c>
+      <c r="J108" s="3" t="n">
+        <v>229.213075343393</v>
       </c>
       <c r="K108" s="2" t="n"/>
     </row>
@@ -4655,12 +4627,12 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>F184</t>
+          <t>F183</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>補足前現金路徑（不補外部資金；擴張・部分變現：②加已到位股權（基準））</t>
+          <t>累計外部資金需求（擴張・部分變現：②加已到位股權（基準））</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -4669,26 +4641,22 @@
         </is>
       </c>
       <c r="E109" s="2" t="n"/>
-      <c r="F109" s="3" t="n">
-        <v>117.691580641443</v>
-      </c>
-      <c r="G109" s="3" t="n">
-        <v>99.56522744598161</v>
-      </c>
-      <c r="H109" s="3" t="n">
-        <v>87.0401219404262</v>
-      </c>
-      <c r="I109" s="3" t="n">
-        <v>136.478108480358</v>
-      </c>
-      <c r="J109" s="3" t="n">
-        <v>240.198645457163</v>
-      </c>
-      <c r="K109" s="2" t="inlineStr">
-        <is>
-          <t>可為負；谷底＝最小值</t>
-        </is>
-      </c>
+      <c r="F109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="2" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -4698,26 +4666,40 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>F185</t>
+          <t>F184</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>缺口年標示（擴張・部分變現：②加已到位股權（基準））</t>
+          <t>補足前現金路徑（不補外部資金；擴張・部分變現：②加已到位股權（基準））</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>$B</t>
         </is>
       </c>
       <c r="E110" s="2" t="n"/>
-      <c r="F110" s="2" t="n"/>
-      <c r="G110" s="2" t="n"/>
-      <c r="H110" s="2" t="n"/>
-      <c r="I110" s="2" t="n"/>
-      <c r="J110" s="2" t="n"/>
-      <c r="K110" s="2" t="n"/>
+      <c r="F110" s="3" t="n">
+        <v>117.691580641443</v>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>99.18786119083759</v>
+      </c>
+      <c r="H110" s="3" t="n">
+        <v>84.22806806837229</v>
+      </c>
+      <c r="I110" s="3" t="n">
+        <v>129.450895133038</v>
+      </c>
+      <c r="J110" s="3" t="n">
+        <v>229.213075343393</v>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>可為負；谷底＝最小值</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -4727,12 +4709,12 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>F186</t>
+          <t>F185</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>最低現金缺口首次出現年（擴張・部分變現：②加已到位股權（基準）；無則「無」）</t>
+          <t>缺口年標示（擴張・部分變現：②加已到位股權（基準））</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -4740,11 +4722,7 @@
           <t>年</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>無</t>
-        </is>
-      </c>
+      <c r="E111" s="2" t="n"/>
       <c r="F111" s="2" t="n"/>
       <c r="G111" s="2" t="n"/>
       <c r="H111" s="2" t="n"/>
@@ -4760,21 +4738,23 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>F187</t>
+          <t>F186</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>累計外部資金需求（擴張・部分變現：②加已到位股權（基準）；2026–2030）</t>
+          <t>最低現金缺口首次出現年（擴張・部分變現：②加已到位股權（基準）；無則「無」）</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>$B</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="n">
-        <v>0</v>
+          <t>年</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
       </c>
       <c r="F112" s="2" t="n"/>
       <c r="G112" s="2" t="n"/>
@@ -4791,12 +4771,12 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>F188</t>
+          <t>F187</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>現金谷底（擴張・部分變現：②加已到位股權（基準）；補足前路徑 2026–2030 最小值）</t>
+          <t>累計外部資金需求（擴張・部分變現：②加已到位股權（基準）；2026–2030）</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -4804,19 +4784,15 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E113" s="3" t="n">
-        <v>87.0401219404262</v>
+      <c r="E113" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F113" s="2" t="n"/>
       <c r="G113" s="2" t="n"/>
       <c r="H113" s="2" t="n"/>
       <c r="I113" s="2" t="n"/>
       <c r="J113" s="2" t="n"/>
-      <c r="K113" s="2" t="inlineStr">
-        <is>
-          <t>負＝需外部補足的金額（不含最低現金）</t>
-        </is>
-      </c>
+      <c r="K113" s="2" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -4826,12 +4802,12 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>F189</t>
+          <t>F188</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>股權流入（擴張・部分變現：③再加條件式與談判中）</t>
+          <t>現金谷底（擴張・部分變現：②加已到位股權（基準）；補足前路徑 2026–2030 最小值）</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -4839,23 +4815,19 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E114" s="2" t="n"/>
-      <c r="F114" s="2" t="n">
-        <v>210</v>
-      </c>
-      <c r="G114" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="H114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K114" s="2" t="n"/>
+      <c r="E114" s="3" t="n">
+        <v>84.22806806837229</v>
+      </c>
+      <c r="F114" s="2" t="n"/>
+      <c r="G114" s="2" t="n"/>
+      <c r="H114" s="2" t="n"/>
+      <c r="I114" s="2" t="n"/>
+      <c r="J114" s="2" t="n"/>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>負＝需外部補足的金額（不含最低現金）</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -4865,12 +4837,12 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>F190</t>
+          <t>F189</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>補足前年底現金（擴張・部分變現：③再加條件式與談判中）</t>
+          <t>股權流入（擴張・部分變現：③再加條件式與談判中）</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -4879,20 +4851,20 @@
         </is>
       </c>
       <c r="E115" s="2" t="n"/>
-      <c r="F115" s="3" t="n">
-        <v>227.691580641443</v>
-      </c>
-      <c r="G115" s="3" t="n">
-        <v>259.565227445982</v>
-      </c>
-      <c r="H115" s="3" t="n">
-        <v>247.040121940426</v>
-      </c>
-      <c r="I115" s="3" t="n">
-        <v>296.478108480358</v>
-      </c>
-      <c r="J115" s="3" t="n">
-        <v>400.198645457163</v>
+      <c r="F115" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="K115" s="2" t="n"/>
     </row>
@@ -4904,12 +4876,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>F191</t>
+          <t>F190</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>當年外部資金需求（擴張・部分變現：③再加條件式與談判中）</t>
+          <t>補足前年底現金（擴張・部分變現：③再加條件式與談判中）</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -4918,20 +4890,20 @@
         </is>
       </c>
       <c r="E116" s="2" t="n"/>
-      <c r="F116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" s="2" t="n">
-        <v>0</v>
+      <c r="F116" s="3" t="n">
+        <v>227.691580641443</v>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>259.187861190838</v>
+      </c>
+      <c r="H116" s="3" t="n">
+        <v>244.228068068372</v>
+      </c>
+      <c r="I116" s="3" t="n">
+        <v>289.450895133038</v>
+      </c>
+      <c r="J116" s="3" t="n">
+        <v>389.213075343393</v>
       </c>
       <c r="K116" s="2" t="n"/>
     </row>
@@ -4943,12 +4915,12 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>F192</t>
+          <t>F191</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>年底現金（擴張・部分變現：③再加條件式與談判中）</t>
+          <t>當年外部資金需求（擴張・部分變現：③再加條件式與談判中）</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -4956,23 +4928,21 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E117" s="3" t="n">
-        <v>20.28</v>
-      </c>
-      <c r="F117" s="3" t="n">
-        <v>227.691580641443</v>
-      </c>
-      <c r="G117" s="3" t="n">
-        <v>259.565227445982</v>
-      </c>
-      <c r="H117" s="3" t="n">
-        <v>247.040121940426</v>
-      </c>
-      <c r="I117" s="3" t="n">
-        <v>296.478108480358</v>
-      </c>
-      <c r="J117" s="3" t="n">
-        <v>400.198645457163</v>
+      <c r="E117" s="2" t="n"/>
+      <c r="F117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="K117" s="2" t="n"/>
     </row>
@@ -4984,12 +4954,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>F193</t>
+          <t>F192</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>累計外部資金需求（擴張・部分變現：③再加條件式與談判中）</t>
+          <t>年底現金（擴張・部分變現：③再加條件式與談判中）</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -4997,21 +4967,23 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E118" s="2" t="n"/>
-      <c r="F118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" s="2" t="n">
-        <v>0</v>
+      <c r="E118" s="3" t="n">
+        <v>20.28</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>227.691580641443</v>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>259.187861190838</v>
+      </c>
+      <c r="H118" s="3" t="n">
+        <v>244.228068068372</v>
+      </c>
+      <c r="I118" s="3" t="n">
+        <v>289.450895133038</v>
+      </c>
+      <c r="J118" s="3" t="n">
+        <v>389.213075343393</v>
       </c>
       <c r="K118" s="2" t="n"/>
     </row>
@@ -5023,12 +4995,12 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>F194</t>
+          <t>F193</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>補足前現金路徑（不補外部資金；擴張・部分變現：③再加條件式與談判中）</t>
+          <t>累計外部資金需求（擴張・部分變現：③再加條件式與談判中）</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -5037,26 +5009,22 @@
         </is>
       </c>
       <c r="E119" s="2" t="n"/>
-      <c r="F119" s="3" t="n">
-        <v>227.691580641443</v>
-      </c>
-      <c r="G119" s="3" t="n">
-        <v>259.565227445982</v>
-      </c>
-      <c r="H119" s="3" t="n">
-        <v>247.040121940426</v>
-      </c>
-      <c r="I119" s="3" t="n">
-        <v>296.478108480358</v>
-      </c>
-      <c r="J119" s="3" t="n">
-        <v>400.198645457163</v>
-      </c>
-      <c r="K119" s="2" t="inlineStr">
-        <is>
-          <t>可為負；谷底＝最小值</t>
-        </is>
-      </c>
+      <c r="F119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" s="2" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -5066,26 +5034,40 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>F195</t>
+          <t>F194</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>缺口年標示（擴張・部分變現：③再加條件式與談判中）</t>
+          <t>補足前現金路徑（不補外部資金；擴張・部分變現：③再加條件式與談判中）</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>$B</t>
         </is>
       </c>
       <c r="E120" s="2" t="n"/>
-      <c r="F120" s="2" t="n"/>
-      <c r="G120" s="2" t="n"/>
-      <c r="H120" s="2" t="n"/>
-      <c r="I120" s="2" t="n"/>
-      <c r="J120" s="2" t="n"/>
-      <c r="K120" s="2" t="n"/>
+      <c r="F120" s="3" t="n">
+        <v>227.691580641443</v>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>259.187861190838</v>
+      </c>
+      <c r="H120" s="3" t="n">
+        <v>244.228068068372</v>
+      </c>
+      <c r="I120" s="3" t="n">
+        <v>289.450895133038</v>
+      </c>
+      <c r="J120" s="3" t="n">
+        <v>389.213075343393</v>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>可為負；谷底＝最小值</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -5095,12 +5077,12 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>F196</t>
+          <t>F195</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>最低現金缺口首次出現年（擴張・部分變現：③再加條件式與談判中；無則「無」）</t>
+          <t>缺口年標示（擴張・部分變現：③再加條件式與談判中）</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -5108,11 +5090,7 @@
           <t>年</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
-        <is>
-          <t>無</t>
-        </is>
-      </c>
+      <c r="E121" s="2" t="n"/>
       <c r="F121" s="2" t="n"/>
       <c r="G121" s="2" t="n"/>
       <c r="H121" s="2" t="n"/>
@@ -5128,21 +5106,23 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>F197</t>
+          <t>F196</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>累計外部資金需求（擴張・部分變現：③再加條件式與談判中；2026–2030）</t>
+          <t>最低現金缺口首次出現年（擴張・部分變現：③再加條件式與談判中；無則「無」）</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>$B</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="n">
-        <v>0</v>
+          <t>年</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
       </c>
       <c r="F122" s="2" t="n"/>
       <c r="G122" s="2" t="n"/>
@@ -5159,12 +5139,12 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>F198</t>
+          <t>F197</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>現金谷底（擴張・部分變現：③再加條件式與談判中；補足前路徑 2026–2030 最小值）</t>
+          <t>累計外部資金需求（擴張・部分變現：③再加條件式與談判中；2026–2030）</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -5172,19 +5152,15 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E123" s="3" t="n">
-        <v>227.691580641443</v>
+      <c r="E123" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F123" s="2" t="n"/>
       <c r="G123" s="2" t="n"/>
       <c r="H123" s="2" t="n"/>
       <c r="I123" s="2" t="n"/>
       <c r="J123" s="2" t="n"/>
-      <c r="K123" s="2" t="inlineStr">
-        <is>
-          <t>負＝需外部補足的金額（不含最低現金）</t>
-        </is>
-      </c>
+      <c r="K123" s="2" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -5194,30 +5170,32 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>F199</t>
+          <t>F198</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>自由現金流轉正年標示（擴張・完全變現）</t>
+          <t>現金谷底（擴張・部分變現：③再加條件式與談判中；補足前路徑 2026–2030 最小值）</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>年</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="n"/>
+          <t>$B</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>227.691580641443</v>
+      </c>
       <c r="F124" s="2" t="n"/>
       <c r="G124" s="2" t="n"/>
       <c r="H124" s="2" t="n"/>
-      <c r="I124" s="2" t="n">
-        <v>2029</v>
-      </c>
-      <c r="J124" s="2" t="n">
-        <v>2030</v>
-      </c>
-      <c r="K124" s="2" t="n"/>
+      <c r="I124" s="2" t="n"/>
+      <c r="J124" s="2" t="n"/>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>負＝需外部補足的金額（不含最低現金）</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -5227,12 +5205,12 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>F200</t>
+          <t>F199</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>營運自由現金流首次轉正年（擴張・完全變現；無則「無」）</t>
+          <t>自由現金流轉正年標示（擴張・完全變現）</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -5240,19 +5218,17 @@
           <t>年</t>
         </is>
       </c>
-      <c r="E125" s="2" t="n">
-        <v>2029</v>
-      </c>
+      <c r="E125" s="2" t="n"/>
       <c r="F125" s="2" t="n"/>
       <c r="G125" s="2" t="n"/>
       <c r="H125" s="2" t="n"/>
-      <c r="I125" s="2" t="n"/>
-      <c r="J125" s="2" t="n"/>
-      <c r="K125" s="2" t="inlineStr">
-        <is>
-          <t>第一個自給年；不代表其後每年皆為正</t>
-        </is>
-      </c>
+      <c r="I125" s="2" t="n">
+        <v>2029</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>2030</v>
+      </c>
+      <c r="K125" s="2" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -5262,36 +5238,32 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>F201</t>
+          <t>F200</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>補足前年底現金（擴張・完全變現：①營運自給（無任何融資））</t>
+          <t>營運自由現金流首次轉正年（擴張・完全變現；無則「無」）</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>$B</t>
-        </is>
-      </c>
-      <c r="E126" s="2" t="n"/>
-      <c r="F126" s="3" t="n">
-        <v>-2.58841935855733</v>
-      </c>
-      <c r="G126" s="3" t="n">
-        <v>-14.1496268340611</v>
-      </c>
-      <c r="H126" s="3" t="n">
-        <v>-7.60987172286505</v>
-      </c>
-      <c r="I126" s="3" t="n">
-        <v>66.9558079679157</v>
-      </c>
-      <c r="J126" s="3" t="n">
-        <v>215.313949054257</v>
-      </c>
-      <c r="K126" s="2" t="n"/>
+          <t>年</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>2029</v>
+      </c>
+      <c r="F126" s="2" t="n"/>
+      <c r="G126" s="2" t="n"/>
+      <c r="H126" s="2" t="n"/>
+      <c r="I126" s="2" t="n"/>
+      <c r="J126" s="2" t="n"/>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>第一個自給年；不代表其後每年皆為正</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -5301,12 +5273,12 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>F202</t>
+          <t>F201</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>當年外部資金需求（擴張・完全變現：①營運自給（無任何融資））</t>
+          <t>補足前年底現金（擴張・完全變現：①營運自給（無任何融資））</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -5316,19 +5288,19 @@
       </c>
       <c r="E127" s="2" t="n"/>
       <c r="F127" s="3" t="n">
-        <v>6.56514571995733</v>
+        <v>-2.58841935855733</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>19.0648606167515</v>
+        <v>-14.5269930892051</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>13.4319661384618</v>
-      </c>
-      <c r="I127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J127" s="2" t="n">
-        <v>0</v>
+        <v>-10.0445593397749</v>
+      </c>
+      <c r="I127" s="3" t="n">
+        <v>63.2573281494455</v>
+      </c>
+      <c r="J127" s="3" t="n">
+        <v>209.664987652008</v>
       </c>
       <c r="K127" s="2" t="n"/>
     </row>
@@ -5340,12 +5312,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>F203</t>
+          <t>F202</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>年底現金（擴張・完全變現：①營運自給（無任何融資））</t>
+          <t>當年外部資金需求（擴張・完全變現：①營運自給（無任何融資））</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -5353,23 +5325,21 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E128" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E128" s="2" t="n"/>
       <c r="F128" s="3" t="n">
-        <v>3.9767263614</v>
+        <v>6.56514571995733</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>4.9152337826904</v>
+        <v>19.4422268718955</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>5.82209441559678</v>
-      </c>
-      <c r="I128" s="3" t="n">
-        <v>66.9558079679157</v>
-      </c>
-      <c r="J128" s="3" t="n">
-        <v>215.313949054257</v>
+        <v>15.8666537553717</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="K128" s="2" t="n"/>
     </row>
@@ -5381,12 +5351,12 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>F204</t>
+          <t>F203</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>累計外部資金需求（擴張・完全變現：①營運自給（無任何融資））</t>
+          <t>年底現金（擴張・完全變現：①營運自給（無任何融資））</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -5394,21 +5364,23 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E129" s="2" t="n"/>
+      <c r="E129" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="F129" s="3" t="n">
-        <v>6.56514571995733</v>
+        <v>3.9767263614</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>25.6300063367088</v>
+        <v>4.9152337826904</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>39.0619724751706</v>
+        <v>5.82209441559678</v>
       </c>
       <c r="I129" s="3" t="n">
-        <v>39.0619724751706</v>
+        <v>63.2573281494455</v>
       </c>
       <c r="J129" s="3" t="n">
-        <v>39.0619724751706</v>
+        <v>209.664987652008</v>
       </c>
       <c r="K129" s="2" t="n"/>
     </row>
@@ -5420,12 +5392,12 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>F205</t>
+          <t>F204</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>補足前現金路徑（不補外部資金；擴張・完全變現：①營運自給（無任何融資））</t>
+          <t>累計外部資金需求（擴張・完全變現：①營運自給（無任何融資））</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -5435,25 +5407,21 @@
       </c>
       <c r="E130" s="2" t="n"/>
       <c r="F130" s="3" t="n">
-        <v>-2.58841935855733</v>
+        <v>6.56514571995733</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>-20.7147725540184</v>
+        <v>26.0073725918528</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>-33.2398780595738</v>
+        <v>41.8740263472245</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>27.893835492745</v>
+        <v>41.8740263472245</v>
       </c>
       <c r="J130" s="3" t="n">
-        <v>176.251976579087</v>
-      </c>
-      <c r="K130" s="2" t="inlineStr">
-        <is>
-          <t>可為負；谷底＝最小值</t>
-        </is>
-      </c>
+        <v>41.8740263472245</v>
+      </c>
+      <c r="K130" s="2" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -5463,32 +5431,40 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>F206</t>
+          <t>F205</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>缺口年標示（擴張・完全變現：①營運自給（無任何融資））</t>
+          <t>補足前現金路徑（不補外部資金；擴張・完全變現：①營運自給（無任何融資））</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>$B</t>
         </is>
       </c>
       <c r="E131" s="2" t="n"/>
-      <c r="F131" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G131" s="2" t="n">
-        <v>2027</v>
-      </c>
-      <c r="H131" s="2" t="n">
-        <v>2028</v>
-      </c>
-      <c r="I131" s="2" t="n"/>
-      <c r="J131" s="2" t="n"/>
-      <c r="K131" s="2" t="n"/>
+      <c r="F131" s="3" t="n">
+        <v>-2.58841935855733</v>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>-21.0921388091624</v>
+      </c>
+      <c r="H131" s="3" t="n">
+        <v>-36.0519319316277</v>
+      </c>
+      <c r="I131" s="3" t="n">
+        <v>21.383301802221</v>
+      </c>
+      <c r="J131" s="3" t="n">
+        <v>167.790961304783</v>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>可為負；谷底＝最小值</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -5498,12 +5474,12 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>F207</t>
+          <t>F206</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>最低現金缺口首次出現年（擴張・完全變現：①營運自給（無任何融資）；無則「無」）</t>
+          <t>缺口年標示（擴張・完全變現：①營運自給（無任何融資））</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -5511,12 +5487,16 @@
           <t>年</t>
         </is>
       </c>
-      <c r="E132" s="2" t="n">
+      <c r="E132" s="2" t="n"/>
+      <c r="F132" s="2" t="n">
         <v>2026</v>
       </c>
-      <c r="F132" s="2" t="n"/>
-      <c r="G132" s="2" t="n"/>
-      <c r="H132" s="2" t="n"/>
+      <c r="G132" s="2" t="n">
+        <v>2027</v>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>2028</v>
+      </c>
       <c r="I132" s="2" t="n"/>
       <c r="J132" s="2" t="n"/>
       <c r="K132" s="2" t="n"/>
@@ -5529,21 +5509,21 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>F208</t>
+          <t>F207</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>累計外部資金需求（擴張・完全變現：①營運自給（無任何融資）；2026–2030）</t>
+          <t>最低現金缺口首次出現年（擴張・完全變現：①營運自給（無任何融資）；無則「無」）</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>$B</t>
-        </is>
-      </c>
-      <c r="E133" s="3" t="n">
-        <v>39.0619724751706</v>
+          <t>年</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>2026</v>
       </c>
       <c r="F133" s="2" t="n"/>
       <c r="G133" s="2" t="n"/>
@@ -5560,12 +5540,12 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>F209</t>
+          <t>F208</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>現金谷底（擴張・完全變現：①營運自給（無任何融資）；補足前路徑 2026–2030 最小值）</t>
+          <t>累計外部資金需求（擴張・完全變現：①營運自給（無任何融資）；2026–2030）</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -5574,18 +5554,14 @@
         </is>
       </c>
       <c r="E134" s="3" t="n">
-        <v>-33.2398780595738</v>
+        <v>41.8740263472245</v>
       </c>
       <c r="F134" s="2" t="n"/>
       <c r="G134" s="2" t="n"/>
       <c r="H134" s="2" t="n"/>
       <c r="I134" s="2" t="n"/>
       <c r="J134" s="2" t="n"/>
-      <c r="K134" s="2" t="inlineStr">
-        <is>
-          <t>負＝需外部補足的金額（不含最低現金）</t>
-        </is>
-      </c>
+      <c r="K134" s="2" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -5595,12 +5571,12 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>F210</t>
+          <t>F209</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>股權流入（擴張・完全變現：②加已到位股權（基準））</t>
+          <t>現金谷底（擴張・完全變現：①營運自給（無任何融資）；補足前路徑 2026–2030 最小值）</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -5608,23 +5584,19 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E135" s="2" t="n"/>
-      <c r="F135" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="G135" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H135" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I135" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J135" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K135" s="2" t="n"/>
+      <c r="E135" s="3" t="n">
+        <v>-36.0519319316277</v>
+      </c>
+      <c r="F135" s="2" t="n"/>
+      <c r="G135" s="2" t="n"/>
+      <c r="H135" s="2" t="n"/>
+      <c r="I135" s="2" t="n"/>
+      <c r="J135" s="2" t="n"/>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>負＝需外部補足的金額（不含最低現金）</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -5634,12 +5606,12 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>F211</t>
+          <t>F210</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>補足前年底現金（擴張・完全變現：②加已到位股權（基準））</t>
+          <t>股權流入（擴張・完全變現：②加已到位股權（基準））</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -5648,20 +5620,20 @@
         </is>
       </c>
       <c r="E136" s="2" t="n"/>
-      <c r="F136" s="3" t="n">
-        <v>117.691580641443</v>
-      </c>
-      <c r="G136" s="3" t="n">
-        <v>99.56522744598161</v>
-      </c>
-      <c r="H136" s="3" t="n">
-        <v>87.0401219404262</v>
-      </c>
-      <c r="I136" s="3" t="n">
-        <v>148.173835492745</v>
-      </c>
-      <c r="J136" s="3" t="n">
-        <v>296.531976579087</v>
+      <c r="F136" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="K136" s="2" t="n"/>
     </row>
@@ -5673,12 +5645,12 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>F212</t>
+          <t>F211</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>當年外部資金需求（擴張・完全變現：②加已到位股權（基準））</t>
+          <t>補足前年底現金（擴張・完全變現：②加已到位股權（基準））</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -5687,20 +5659,20 @@
         </is>
       </c>
       <c r="E137" s="2" t="n"/>
-      <c r="F137" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G137" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H137" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I137" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J137" s="2" t="n">
-        <v>0</v>
+      <c r="F137" s="3" t="n">
+        <v>117.691580641443</v>
+      </c>
+      <c r="G137" s="3" t="n">
+        <v>99.18786119083759</v>
+      </c>
+      <c r="H137" s="3" t="n">
+        <v>84.22806806837229</v>
+      </c>
+      <c r="I137" s="3" t="n">
+        <v>141.663301802221</v>
+      </c>
+      <c r="J137" s="3" t="n">
+        <v>288.070961304783</v>
       </c>
       <c r="K137" s="2" t="n"/>
     </row>
@@ -5712,12 +5684,12 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>F213</t>
+          <t>F212</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>年底現金（擴張・完全變現：②加已到位股權（基準））</t>
+          <t>當年外部資金需求（擴張・完全變現：②加已到位股權（基準））</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -5725,23 +5697,21 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E138" s="3" t="n">
-        <v>20.28</v>
-      </c>
-      <c r="F138" s="3" t="n">
-        <v>117.691580641443</v>
-      </c>
-      <c r="G138" s="3" t="n">
-        <v>99.56522744598161</v>
-      </c>
-      <c r="H138" s="3" t="n">
-        <v>87.0401219404262</v>
-      </c>
-      <c r="I138" s="3" t="n">
-        <v>148.173835492745</v>
-      </c>
-      <c r="J138" s="3" t="n">
-        <v>296.531976579087</v>
+      <c r="E138" s="2" t="n"/>
+      <c r="F138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="K138" s="2" t="n"/>
     </row>
@@ -5753,12 +5723,12 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>F214</t>
+          <t>F213</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>累計外部資金需求（擴張・完全變現：②加已到位股權（基準））</t>
+          <t>年底現金（擴張・完全變現：②加已到位股權（基準））</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -5766,21 +5736,23 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E139" s="2" t="n"/>
-      <c r="F139" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G139" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H139" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I139" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" s="2" t="n">
-        <v>0</v>
+      <c r="E139" s="3" t="n">
+        <v>20.28</v>
+      </c>
+      <c r="F139" s="3" t="n">
+        <v>117.691580641443</v>
+      </c>
+      <c r="G139" s="3" t="n">
+        <v>99.18786119083759</v>
+      </c>
+      <c r="H139" s="3" t="n">
+        <v>84.22806806837229</v>
+      </c>
+      <c r="I139" s="3" t="n">
+        <v>141.663301802221</v>
+      </c>
+      <c r="J139" s="3" t="n">
+        <v>288.070961304783</v>
       </c>
       <c r="K139" s="2" t="n"/>
     </row>
@@ -5792,12 +5764,12 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>F215</t>
+          <t>F214</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>補足前現金路徑（不補外部資金；擴張・完全變現：②加已到位股權（基準））</t>
+          <t>累計外部資金需求（擴張・完全變現：②加已到位股權（基準））</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -5806,26 +5778,22 @@
         </is>
       </c>
       <c r="E140" s="2" t="n"/>
-      <c r="F140" s="3" t="n">
-        <v>117.691580641443</v>
-      </c>
-      <c r="G140" s="3" t="n">
-        <v>99.56522744598161</v>
-      </c>
-      <c r="H140" s="3" t="n">
-        <v>87.0401219404262</v>
-      </c>
-      <c r="I140" s="3" t="n">
-        <v>148.173835492745</v>
-      </c>
-      <c r="J140" s="3" t="n">
-        <v>296.531976579087</v>
-      </c>
-      <c r="K140" s="2" t="inlineStr">
-        <is>
-          <t>可為負；谷底＝最小值</t>
-        </is>
-      </c>
+      <c r="F140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" s="2" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -5835,26 +5803,40 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>F216</t>
+          <t>F215</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>缺口年標示（擴張・完全變現：②加已到位股權（基準））</t>
+          <t>補足前現金路徑（不補外部資金；擴張・完全變現：②加已到位股權（基準））</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>$B</t>
         </is>
       </c>
       <c r="E141" s="2" t="n"/>
-      <c r="F141" s="2" t="n"/>
-      <c r="G141" s="2" t="n"/>
-      <c r="H141" s="2" t="n"/>
-      <c r="I141" s="2" t="n"/>
-      <c r="J141" s="2" t="n"/>
-      <c r="K141" s="2" t="n"/>
+      <c r="F141" s="3" t="n">
+        <v>117.691580641443</v>
+      </c>
+      <c r="G141" s="3" t="n">
+        <v>99.18786119083759</v>
+      </c>
+      <c r="H141" s="3" t="n">
+        <v>84.22806806837229</v>
+      </c>
+      <c r="I141" s="3" t="n">
+        <v>141.663301802221</v>
+      </c>
+      <c r="J141" s="3" t="n">
+        <v>288.070961304783</v>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>可為負；谷底＝最小值</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -5864,12 +5846,12 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>F217</t>
+          <t>F216</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>最低現金缺口首次出現年（擴張・完全變現：②加已到位股權（基準）；無則「無」）</t>
+          <t>缺口年標示（擴張・完全變現：②加已到位股權（基準））</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -5877,11 +5859,7 @@
           <t>年</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
-        <is>
-          <t>無</t>
-        </is>
-      </c>
+      <c r="E142" s="2" t="n"/>
       <c r="F142" s="2" t="n"/>
       <c r="G142" s="2" t="n"/>
       <c r="H142" s="2" t="n"/>
@@ -5897,21 +5875,23 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>F218</t>
+          <t>F217</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>累計外部資金需求（擴張・完全變現：②加已到位股權（基準）；2026–2030）</t>
+          <t>最低現金缺口首次出現年（擴張・完全變現：②加已到位股權（基準）；無則「無」）</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>$B</t>
-        </is>
-      </c>
-      <c r="E143" s="2" t="n">
-        <v>0</v>
+          <t>年</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
       </c>
       <c r="F143" s="2" t="n"/>
       <c r="G143" s="2" t="n"/>
@@ -5928,12 +5908,12 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>F219</t>
+          <t>F218</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>現金谷底（擴張・完全變現：②加已到位股權（基準）；補足前路徑 2026–2030 最小值）</t>
+          <t>累計外部資金需求（擴張・完全變現：②加已到位股權（基準）；2026–2030）</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -5941,19 +5921,15 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E144" s="3" t="n">
-        <v>87.0401219404262</v>
+      <c r="E144" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F144" s="2" t="n"/>
       <c r="G144" s="2" t="n"/>
       <c r="H144" s="2" t="n"/>
       <c r="I144" s="2" t="n"/>
       <c r="J144" s="2" t="n"/>
-      <c r="K144" s="2" t="inlineStr">
-        <is>
-          <t>負＝需外部補足的金額（不含最低現金）</t>
-        </is>
-      </c>
+      <c r="K144" s="2" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -5963,12 +5939,12 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>F220</t>
+          <t>F219</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>股權流入（擴張・完全變現：③再加條件式與談判中）</t>
+          <t>現金谷底（擴張・完全變現：②加已到位股權（基準）；補足前路徑 2026–2030 最小值）</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -5976,23 +5952,19 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E145" s="2" t="n"/>
-      <c r="F145" s="2" t="n">
-        <v>210</v>
-      </c>
-      <c r="G145" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="H145" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I145" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J145" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K145" s="2" t="n"/>
+      <c r="E145" s="3" t="n">
+        <v>84.22806806837229</v>
+      </c>
+      <c r="F145" s="2" t="n"/>
+      <c r="G145" s="2" t="n"/>
+      <c r="H145" s="2" t="n"/>
+      <c r="I145" s="2" t="n"/>
+      <c r="J145" s="2" t="n"/>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>負＝需外部補足的金額（不含最低現金）</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -6002,12 +5974,12 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>F221</t>
+          <t>F220</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>補足前年底現金（擴張・完全變現：③再加條件式與談判中）</t>
+          <t>股權流入（擴張・完全變現：③再加條件式與談判中）</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -6016,20 +5988,20 @@
         </is>
       </c>
       <c r="E146" s="2" t="n"/>
-      <c r="F146" s="3" t="n">
-        <v>227.691580641443</v>
-      </c>
-      <c r="G146" s="3" t="n">
-        <v>259.565227445982</v>
-      </c>
-      <c r="H146" s="3" t="n">
-        <v>247.040121940426</v>
-      </c>
-      <c r="I146" s="3" t="n">
-        <v>308.173835492745</v>
-      </c>
-      <c r="J146" s="3" t="n">
-        <v>456.531976579087</v>
+      <c r="F146" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="G146" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="K146" s="2" t="n"/>
     </row>
@@ -6041,12 +6013,12 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>F222</t>
+          <t>F221</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>當年外部資金需求（擴張・完全變現：③再加條件式與談判中）</t>
+          <t>補足前年底現金（擴張・完全變現：③再加條件式與談判中）</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -6055,20 +6027,20 @@
         </is>
       </c>
       <c r="E147" s="2" t="n"/>
-      <c r="F147" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G147" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H147" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I147" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J147" s="2" t="n">
-        <v>0</v>
+      <c r="F147" s="3" t="n">
+        <v>227.691580641443</v>
+      </c>
+      <c r="G147" s="3" t="n">
+        <v>259.187861190838</v>
+      </c>
+      <c r="H147" s="3" t="n">
+        <v>244.228068068372</v>
+      </c>
+      <c r="I147" s="3" t="n">
+        <v>301.663301802221</v>
+      </c>
+      <c r="J147" s="3" t="n">
+        <v>448.070961304783</v>
       </c>
       <c r="K147" s="2" t="n"/>
     </row>
@@ -6080,12 +6052,12 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>F223</t>
+          <t>F222</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>年底現金（擴張・完全變現：③再加條件式與談判中）</t>
+          <t>當年外部資金需求（擴張・完全變現：③再加條件式與談判中）</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -6093,23 +6065,21 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E148" s="3" t="n">
-        <v>20.28</v>
-      </c>
-      <c r="F148" s="3" t="n">
-        <v>227.691580641443</v>
-      </c>
-      <c r="G148" s="3" t="n">
-        <v>259.565227445982</v>
-      </c>
-      <c r="H148" s="3" t="n">
-        <v>247.040121940426</v>
-      </c>
-      <c r="I148" s="3" t="n">
-        <v>308.173835492745</v>
-      </c>
-      <c r="J148" s="3" t="n">
-        <v>456.531976579087</v>
+      <c r="E148" s="2" t="n"/>
+      <c r="F148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="K148" s="2" t="n"/>
     </row>
@@ -6121,12 +6091,12 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>F224</t>
+          <t>F223</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>累計外部資金需求（擴張・完全變現：③再加條件式與談判中）</t>
+          <t>年底現金（擴張・完全變現：③再加條件式與談判中）</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -6134,21 +6104,23 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E149" s="2" t="n"/>
-      <c r="F149" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G149" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H149" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I149" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J149" s="2" t="n">
-        <v>0</v>
+      <c r="E149" s="3" t="n">
+        <v>20.28</v>
+      </c>
+      <c r="F149" s="3" t="n">
+        <v>227.691580641443</v>
+      </c>
+      <c r="G149" s="3" t="n">
+        <v>259.187861190838</v>
+      </c>
+      <c r="H149" s="3" t="n">
+        <v>244.228068068372</v>
+      </c>
+      <c r="I149" s="3" t="n">
+        <v>301.663301802221</v>
+      </c>
+      <c r="J149" s="3" t="n">
+        <v>448.070961304783</v>
       </c>
       <c r="K149" s="2" t="n"/>
     </row>
@@ -6160,12 +6132,12 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>F225</t>
+          <t>F224</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>補足前現金路徑（不補外部資金；擴張・完全變現：③再加條件式與談判中）</t>
+          <t>累計外部資金需求（擴張・完全變現：③再加條件式與談判中）</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -6174,26 +6146,22 @@
         </is>
       </c>
       <c r="E150" s="2" t="n"/>
-      <c r="F150" s="3" t="n">
-        <v>227.691580641443</v>
-      </c>
-      <c r="G150" s="3" t="n">
-        <v>259.565227445982</v>
-      </c>
-      <c r="H150" s="3" t="n">
-        <v>247.040121940426</v>
-      </c>
-      <c r="I150" s="3" t="n">
-        <v>308.173835492745</v>
-      </c>
-      <c r="J150" s="3" t="n">
-        <v>456.531976579087</v>
-      </c>
-      <c r="K150" s="2" t="inlineStr">
-        <is>
-          <t>可為負；谷底＝最小值</t>
-        </is>
-      </c>
+      <c r="F150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" s="2" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -6203,26 +6171,40 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>F226</t>
+          <t>F225</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>缺口年標示（擴張・完全變現：③再加條件式與談判中）</t>
+          <t>補足前現金路徑（不補外部資金；擴張・完全變現：③再加條件式與談判中）</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>$B</t>
         </is>
       </c>
       <c r="E151" s="2" t="n"/>
-      <c r="F151" s="2" t="n"/>
-      <c r="G151" s="2" t="n"/>
-      <c r="H151" s="2" t="n"/>
-      <c r="I151" s="2" t="n"/>
-      <c r="J151" s="2" t="n"/>
-      <c r="K151" s="2" t="n"/>
+      <c r="F151" s="3" t="n">
+        <v>227.691580641443</v>
+      </c>
+      <c r="G151" s="3" t="n">
+        <v>259.187861190838</v>
+      </c>
+      <c r="H151" s="3" t="n">
+        <v>244.228068068372</v>
+      </c>
+      <c r="I151" s="3" t="n">
+        <v>301.663301802221</v>
+      </c>
+      <c r="J151" s="3" t="n">
+        <v>448.070961304783</v>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>可為負；谷底＝最小值</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -6232,12 +6214,12 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>F227</t>
+          <t>F226</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>最低現金缺口首次出現年（擴張・完全變現：③再加條件式與談判中；無則「無」）</t>
+          <t>缺口年標示（擴張・完全變現：③再加條件式與談判中）</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -6245,11 +6227,7 @@
           <t>年</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t>無</t>
-        </is>
-      </c>
+      <c r="E152" s="2" t="n"/>
       <c r="F152" s="2" t="n"/>
       <c r="G152" s="2" t="n"/>
       <c r="H152" s="2" t="n"/>
@@ -6265,21 +6243,23 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>F228</t>
+          <t>F227</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>累計外部資金需求（擴張・完全變現：③再加條件式與談判中；2026–2030）</t>
+          <t>最低現金缺口首次出現年（擴張・完全變現：③再加條件式與談判中；無則「無」）</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>$B</t>
-        </is>
-      </c>
-      <c r="E153" s="2" t="n">
-        <v>0</v>
+          <t>年</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
       </c>
       <c r="F153" s="2" t="n"/>
       <c r="G153" s="2" t="n"/>
@@ -6296,12 +6276,12 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>F229</t>
+          <t>F228</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>現金谷底（擴張・完全變現：③再加條件式與談判中；補足前路徑 2026–2030 最小值）</t>
+          <t>累計外部資金需求（擴張・完全變現：③再加條件式與談判中；2026–2030）</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -6309,120 +6289,108 @@
           <t>$B</t>
         </is>
       </c>
-      <c r="E154" s="3" t="n">
-        <v>227.691580641443</v>
+      <c r="E154" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F154" s="2" t="n"/>
       <c r="G154" s="2" t="n"/>
       <c r="H154" s="2" t="n"/>
       <c r="I154" s="2" t="n"/>
       <c r="J154" s="2" t="n"/>
-      <c r="K154" s="2" t="inlineStr">
-        <is>
-          <t>負＝需外部補足的金額（不含最低現金）</t>
-        </is>
-      </c>
+      <c r="K154" s="2" t="n"/>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n"/>
-      <c r="B155" s="2" t="n"/>
-      <c r="C155" s="2" t="n"/>
-      <c r="D155" s="2" t="n"/>
-      <c r="E155" s="2" t="n"/>
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Funding</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>F229</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>現金谷底（擴張・完全變現：③再加條件式與談判中；補足前路徑 2026–2030 最小值）</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>$B</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>227.691580641443</v>
+      </c>
       <c r="F155" s="2" t="n"/>
       <c r="G155" s="2" t="n"/>
       <c r="H155" s="2" t="n"/>
       <c r="I155" s="2" t="n"/>
       <c r="J155" s="2" t="n"/>
-      <c r="K155" s="2" t="n"/>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>負＝需外部補足的金額（不含最低現金）</t>
+        </is>
+      </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>Inputs（新增）</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>參數</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
-        <is>
-          <t>單位</t>
-        </is>
-      </c>
-      <c r="E156" s="2" t="inlineStr">
-        <is>
-          <t>值</t>
-        </is>
-      </c>
-      <c r="F156" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="G156" s="2" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>標記</t>
-        </is>
-      </c>
-      <c r="I156" s="2" t="inlineStr">
-        <is>
-          <t>依據</t>
-        </is>
-      </c>
+      <c r="A156" s="2" t="n"/>
+      <c r="B156" s="2" t="n"/>
+      <c r="C156" s="2" t="n"/>
+      <c r="D156" s="2" t="n"/>
+      <c r="E156" s="2" t="n"/>
+      <c r="F156" s="2" t="n"/>
+      <c r="G156" s="2" t="n"/>
+      <c r="H156" s="2" t="n"/>
+      <c r="I156" s="2" t="n"/>
       <c r="J156" s="2" t="n"/>
       <c r="K156" s="2" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Inputs</t>
+          <t>Inputs（新增）</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>INP_187</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>U2 新法開關（v0.1.3；1＝Nscale、Lambda 供給 GW 用揭露容量 460／350 MW，付款＝MIN(揭露 GW × 合約價</t>
+          <t>參數</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>開關</t>
-        </is>
-      </c>
-      <c r="E157" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F157" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G157" s="2" t="n">
-        <v>1</v>
+          <t>單位</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>標記</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>Andy 2026-10-22 同意 v0.1.1 時的預設改法（工作單 20261022 A 段步驟 2）；SRC_ANT 的 cmp_nscale_mw、cmp_lambda_mw、cmp_s1_nscale_lambda_86</t>
+          <t>依據</t>
         </is>
       </c>
       <c r="J157" s="2" t="n"/>
@@ -6436,12 +6404,12 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>INP_188</t>
+          <t>INP_187</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>資金第 1 層（營運自由現金流自給）是否計入 2025 年底現金（1＝計入；0＝不計，純營運現金流）</t>
+          <t>U2 新法開關（v0.1.3；1＝Nscale、Lambda 供給 GW 取揭露容量 460／350 MW；付款路徑不變＝『最高 86』按 MW 比例分攤的年付款；0＝v0.1.1／v0.1.2 的金額回推 GW；u2_switch＝0 時本開關無作用）</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -6450,7 +6418,7 @@
         </is>
       </c>
       <c r="E158" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F158" s="2" t="n">
         <v>0</v>
@@ -6465,7 +6433,7 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>工作單 20261022 A 段步驟 3：『不靠任何融資時的現金路徑』；2025 年底現金 20.28 是過去融資所得，故第 1 層預設不計；替代＝計入（Funding 第十節）</t>
+          <t>Andy 2026-10-22 同意 v0.1.1 時的預設改法；chat 端更正 A 段工作單步驟 2（容量用揭露值、付款維持金額攤提）；SRC_ANT 的 cmp_nscale_mw、cmp_lambda_mw、cmp_s1_nscale_lambda_86</t>
         </is>
       </c>
       <c r="J158" s="2" t="n"/>
@@ -6479,36 +6447,36 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>INP_189</t>
+          <t>INP_188</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>持續擴張情境：每個追加年的追加金額＝當年基準合約付款 ×（本比例）</t>
+          <t>資金第 1 層（營運自由現金流自給）是否計入 2025 年底現金（1＝計入；0＝不計，純營運現金流）</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>比例</t>
-        </is>
-      </c>
-      <c r="E159" s="3" t="n">
-        <v>0.3</v>
+          <t>開關</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F159" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G159" s="3" t="n">
-        <v>0.6</v>
+      <c r="G159" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>Assumed</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>外部驗收報告 Priority 3（2029–2030 每年追加算力）；工作單 20261022 A 段步驟 4 例：2029、2030 各追加當年合約付款的 30%（區間 0–60%）；無公開依據</t>
+          <t>工作單 20261022 A 段步驟 3：『不靠任何融資時的現金路徑』；2025 年底現金 20.28 是過去融資所得，故第 1 層預設不計；替代＝計入（Funding 第十節）</t>
         </is>
       </c>
       <c r="J159" s="2" t="n"/>
@@ -6522,36 +6490,36 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>INP_190</t>
+          <t>INP_189</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>持續擴張情境：第一個追加年</t>
+          <t>持續擴張情境：每個追加年的追加金額＝當年基準合約付款 ×（本比例）</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>年</t>
-        </is>
-      </c>
-      <c r="E160" s="2" t="n">
-        <v>2029</v>
+          <t>比例</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>0.3</v>
       </c>
       <c r="F160" s="2" t="n">
-        <v>2029</v>
-      </c>
-      <c r="G160" s="2" t="n">
-        <v>2029</v>
+        <v>0</v>
+      </c>
+      <c r="G160" s="3" t="n">
+        <v>0.6</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Assumed</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>工作單 20261022 A 段步驟 4：2029、2030</t>
+          <t>外部驗收報告 Priority 3（2029–2030 每年追加算力）；工作單 20261022 A 段步驟 4 例：2029、2030 各追加當年合約付款的 30%（區間 0–60%）；無公開依據</t>
         </is>
       </c>
       <c r="J160" s="2" t="n"/>
@@ -6565,12 +6533,12 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>INP_191</t>
+          <t>INP_190</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>持續擴張情境：最後一個追加年</t>
+          <t>持續擴張情境：第一個追加年</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -6579,13 +6547,13 @@
         </is>
       </c>
       <c r="E161" s="2" t="n">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="F161" s="2" t="n">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="G161" s="2" t="n">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -6608,27 +6576,27 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>INP_192</t>
+          <t>INP_191</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>持續擴張情境：變現比例（無需求）</t>
+          <t>持續擴張情境：最後一個追加年</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>比例</t>
+          <t>年</t>
         </is>
       </c>
       <c r="E162" s="2" t="n">
-        <v>0</v>
+        <v>2030</v>
       </c>
       <c r="F162" s="2" t="n">
-        <v>0</v>
+        <v>2030</v>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0</v>
+        <v>2030</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -6637,7 +6605,7 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>工作單 20261022 A 段步驟 4：變現比例 3 檔之 0（新增算力沒有對應營收）</t>
+          <t>工作單 20261022 A 段步驟 4：2029、2030</t>
         </is>
       </c>
       <c r="J162" s="2" t="n"/>
@@ -6651,12 +6619,12 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>INP_193</t>
+          <t>INP_192</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>持續擴張情境：變現比例（部分變現）</t>
+          <t>持續擴張情境：變現比例（無需求）</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
@@ -6664,23 +6632,23 @@
           <t>比例</t>
         </is>
       </c>
-      <c r="E163" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F163" s="3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G163" s="3" t="n">
-        <v>0.75</v>
+      <c r="E163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G163" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>Assumed</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>工作單 20261022 A 段步驟 4：變現比例 3 檔之 0.5；無實證依據</t>
+          <t>工作單 20261022 A 段步驟 4：變現比例 3 檔之 0（新增算力沒有對應營收）</t>
         </is>
       </c>
       <c r="J163" s="2" t="n"/>
@@ -6694,12 +6662,12 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>INP_194</t>
+          <t>INP_193</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>持續擴張情境：變現比例（完全變現）</t>
+          <t>持續擴張情境：變現比例（部分變現）</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
@@ -6707,72 +6675,78 @@
           <t>比例</t>
         </is>
       </c>
-      <c r="E164" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F164" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G164" s="2" t="n">
-        <v>1</v>
+      <c r="E164" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F164" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G164" s="3" t="n">
+        <v>0.75</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Assumed</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>工作單 20261022 A 段步驟 4：變現比例 3 檔之 1（新增 GW 的每 GW 營收 ＝ 當年基準每 VR 等值 GW 營收淨額）</t>
+          <t>工作單 20261022 A 段步驟 4：變現比例 3 檔之 0.5；無實證依據</t>
         </is>
       </c>
       <c r="J164" s="2" t="n"/>
       <c r="K164" s="2" t="n"/>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n"/>
-      <c r="B165" s="2" t="n"/>
-      <c r="C165" s="2" t="n"/>
-      <c r="D165" s="2" t="n"/>
-      <c r="E165" s="2" t="n"/>
-      <c r="F165" s="2" t="n"/>
-      <c r="G165" s="2" t="n"/>
-      <c r="H165" s="2" t="n"/>
-      <c r="I165" s="2" t="n"/>
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Inputs</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>INP_194</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>持續擴張情境：變現比例（完全變現）</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>比例</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F165" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G165" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>工作單 20261022 A 段步驟 4：變現比例 3 檔之 1（新增 GW 的每 GW 營收 ＝ 當年基準每 VR 等值 GW 營收淨額）</t>
+        </is>
+      </c>
       <c r="J165" s="2" t="n"/>
       <c r="K165" s="2" t="n"/>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>Checks（新增）</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>檢查項</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
-        <is>
-          <t>值</t>
-        </is>
-      </c>
-      <c r="E166" s="2" t="inlineStr">
-        <is>
-          <t>期望</t>
-        </is>
-      </c>
-      <c r="F166" s="2" t="inlineStr">
-        <is>
-          <t>狀態</t>
-        </is>
-      </c>
+      <c r="A166" s="2" t="n"/>
+      <c r="B166" s="2" t="n"/>
+      <c r="C166" s="2" t="n"/>
+      <c r="D166" s="2" t="n"/>
+      <c r="E166" s="2" t="n"/>
+      <c r="F166" s="2" t="n"/>
       <c r="G166" s="2" t="n"/>
       <c r="H166" s="2" t="n"/>
       <c r="I166" s="2" t="n"/>
@@ -6782,28 +6756,32 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>Checks</t>
+          <t>Checks（新增）</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>C127</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>v0.1.3 U2 新法：付款超出年上限或揭露容量 × 合約價的金額（各年最大；$B）</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E167" s="2" t="n">
-        <v>0</v>
+          <t>檢查項</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>期望</t>
+        </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>狀態</t>
         </is>
       </c>
       <c r="G167" s="2" t="n"/>
@@ -6820,21 +6798,23 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>C128</t>
+          <t>C127</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>v0.1.3 U2 新法：年上限實際約束的合約年數（info）</t>
+          <t>v0.1.3 U2 新法：合約實付與『最高 86』年付款列的差（各年最大；$B）</t>
         </is>
       </c>
       <c r="D168" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E168" s="2" t="n"/>
+      <c r="E168" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>INFO</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="G168" s="2" t="n"/>
@@ -6957,7 +6937,7 @@
         </is>
       </c>
       <c r="D172" s="3" t="n">
-        <v>39.0619724751706</v>
+        <v>41.8740263472245</v>
       </c>
       <c r="E172" s="2" t="n"/>
       <c r="F172" s="2" t="inlineStr">
@@ -6988,7 +6968,7 @@
         </is>
       </c>
       <c r="D173" s="3" t="n">
-        <v>-33.2398780595738</v>
+        <v>-36.0519319316277</v>
       </c>
       <c r="E173" s="2" t="n"/>
       <c r="F173" s="2" t="inlineStr">
@@ -7019,7 +6999,7 @@
         </is>
       </c>
       <c r="D174" s="3" t="n">
-        <v>87.0401219404262</v>
+        <v>84.22806806837229</v>
       </c>
       <c r="E174" s="2" t="n"/>
       <c r="F174" s="2" t="inlineStr">
@@ -7081,7 +7061,7 @@
         </is>
       </c>
       <c r="D176" s="3" t="n">
-        <v>4.72569908457296</v>
+        <v>4.13475145036218</v>
       </c>
       <c r="E176" s="2" t="n"/>
       <c r="F176" s="2" t="inlineStr">
@@ -7112,7 +7092,7 @@
         </is>
       </c>
       <c r="D177" s="3" t="n">
-        <v>8.719885378457599</v>
+        <v>8.251760587277341</v>
       </c>
       <c r="E177" s="2" t="n"/>
       <c r="F177" s="2" t="inlineStr">
@@ -7143,7 +7123,7 @@
         </is>
       </c>
       <c r="D178" s="3" t="n">
-        <v>12.7140716723422</v>
+        <v>12.3687697241925</v>
       </c>
       <c r="E178" s="2" t="n"/>
       <c r="F178" s="2" t="inlineStr">
@@ -7187,6 +7167,99 @@
       <c r="I179" s="2" t="n"/>
       <c r="J179" s="2" t="n"/>
       <c r="K179" s="2" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Checks</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>C140</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>v0.1.3 U2：Nscale 隱含每 GW 年付款（$B/GW/年；對照通用合約價）</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="n">
+        <v>19.304152637486</v>
+      </c>
+      <c r="E180" s="2" t="n"/>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="n"/>
+      <c r="H180" s="2" t="n"/>
+      <c r="I180" s="2" t="n"/>
+      <c r="J180" s="2" t="n"/>
+      <c r="K180" s="2" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Checks</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>C141</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>v0.1.3 U2：Lambda 隱含每 GW 年付款（$B/GW/年）</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="n">
+        <v>14.156378600823</v>
+      </c>
+      <c r="E181" s="2" t="n"/>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="n"/>
+      <c r="H181" s="2" t="n"/>
+      <c r="I181" s="2" t="n"/>
+      <c r="J181" s="2" t="n"/>
+      <c r="K181" s="2" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Checks</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>C142</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>v0.1.3 U2：兩約合計隱含每 GW 年付款（$B/GW/年）</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="n">
+        <v>17.0798058315205</v>
+      </c>
+      <c r="E182" s="2" t="n"/>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="n"/>
+      <c r="H182" s="2" t="n"/>
+      <c r="I182" s="2" t="n"/>
+      <c r="J182" s="2" t="n"/>
+      <c r="K182" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7310,16 +7383,16 @@
         <v>-5.36501172129409</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-4.82838767297759</v>
+        <v>-4.91025301987502</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-2.36820322078253</v>
+        <v>-2.69802276504026</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>5.90721186926193</v>
+        <v>5.37896992727052</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>12.1331557583687</v>
+        <v>11.6019174208063</v>
       </c>
       <c r="I3" s="2" t="n"/>
     </row>
@@ -7341,16 +7414,16 @@
         <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.05966779589762972</v>
+        <v>-0.02219755099979981</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2649483815456501</v>
+        <v>-0.06487116271207993</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.74168424562352</v>
+        <v>0.2134423036321094</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.994119960363399</v>
+        <v>0.4628816228009995</v>
       </c>
       <c r="I4" s="2" t="n"/>
     </row>
@@ -7496,16 +7569,16 @@
         <v>47.955115360999</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>21.3457875836466</v>
+        <v>21.427652930544</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>17.8591672754647</v>
+        <v>18.1889868197224</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>14.1841425062992</v>
+        <v>14.7123844482906</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>13.892597534054</v>
+        <v>14.4238358716164</v>
       </c>
       <c r="I9" s="2" t="n"/>
     </row>
@@ -7527,16 +7600,16 @@
         <v>0</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.01500164077240029</v>
+        <v>0.09686698766979873</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.1075158032565007</v>
+        <v>0.4373353475141997</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.05555853858829884</v>
+        <v>0.5838004805796988</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.0442293470545998</v>
+        <v>0.575467684617001</v>
       </c>
       <c r="I10" s="2" t="n"/>
     </row>
@@ -7589,16 +7662,16 @@
         <v>0.888124307888594</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.773801380995813</v>
+        <v>0.770845036748019</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.867395652649717</v>
+        <v>0.851667231837521</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1.41646591372292</v>
+        <v>1.36560830409074</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>1.87335400947358</v>
+        <v>1.80435728221484</v>
       </c>
       <c r="I12" s="2" t="n"/>
     </row>
@@ -7620,16 +7693,16 @@
         <v>0</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.002956344247794007</v>
+        <v>0</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.01572842081219594</v>
+        <v>0</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.05085760963218</v>
+        <v>0</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.06899672725874018</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2" t="n"/>
     </row>
@@ -8057,13 +8130,13 @@
         <v>0</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2.76</v>
+        <v>4.43995510662177</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>5.52</v>
+        <v>8.87991021324355</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>5.52</v>
+        <v>8.87991021324355</v>
       </c>
       <c r="I27" s="2" t="n"/>
     </row>
@@ -8088,13 +8161,13 @@
         <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>-1.679955106621771</v>
+        <v>0</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>-3.35991021324355</v>
+        <v>0</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>-3.35991021324355</v>
+        <v>0</v>
       </c>
       <c r="I28" s="2" t="n"/>
     </row>
@@ -8147,16 +8220,16 @@
         <v>0</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>2.1</v>
+        <v>2.47736625514403</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>4.2</v>
+        <v>4.95473251028807</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>4.2</v>
+        <v>4.95473251028807</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>4.2</v>
+        <v>4.95473251028807</v>
       </c>
       <c r="I30" s="2" t="n"/>
     </row>
@@ -8178,16 +8251,16 @@
         <v>0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0.3773662551440298</v>
+        <v>0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-0.7547325102880702</v>
+        <v>0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0.7547325102880702</v>
+        <v>0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-0.7547325102880702</v>
+        <v>0</v>
       </c>
       <c r="I31" s="2" t="n"/>
     </row>
@@ -8240,16 +8313,16 @@
         <v>25.7535018893387</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>69.64479041426409</v>
+        <v>70.0221566694081</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>100.380377049851</v>
+        <v>102.815064666761</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>93.1403770498507</v>
+        <v>97.2550197733824</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>88.1403770498507</v>
+        <v>92.2550197733824</v>
       </c>
       <c r="I33" s="2" t="n"/>
     </row>
@@ -8271,16 +8344,16 @@
         <v>0</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>-0.3773662551440111</v>
+        <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>-2.434687616909997</v>
+        <v>0</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>-4.114642723531702</v>
+        <v>0</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>-4.114642723531702</v>
+        <v>0</v>
       </c>
       <c r="I34" s="2" t="n"/>
     </row>
@@ -8333,16 +8406,16 @@
         <v>42.4201685560054</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>86.31145708093079</v>
+        <v>86.6888233360748</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>117.047043716517</v>
+        <v>119.481731333427</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>93.1403770498507</v>
+        <v>97.2550197733824</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>88.1403770498507</v>
+        <v>92.2550197733824</v>
       </c>
       <c r="I36" s="2" t="n"/>
     </row>
@@ -8364,16 +8437,16 @@
         <v>0</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-0.3773662551440111</v>
+        <v>0</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>-2.434687616910011</v>
+        <v>0</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>-4.114642723531702</v>
+        <v>0</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>-4.114642723531702</v>
+        <v>0</v>
       </c>
       <c r="I37" s="2" t="n"/>
     </row>
@@ -8519,16 +8592,16 @@
         <v>-2.58841935855733</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>-18.1263531954611</v>
+        <v>-18.5037194506051</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>-12.5251055055554</v>
+        <v>-14.9597931224653</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>51.7133160850224</v>
+        <v>47.5986733614907</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>100.246102539702</v>
+        <v>96.13145981617021</v>
       </c>
       <c r="I42" s="2" t="n"/>
     </row>
@@ -8550,16 +8623,16 @@
         <v>0</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>0.3773662551440005</v>
+        <v>0</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>2.434687616909899</v>
+        <v>0</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>4.114642723531702</v>
+        <v>0</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>4.114642723531787</v>
+        <v>0</v>
       </c>
       <c r="I43" s="2" t="n"/>
     </row>
@@ -8612,16 +8685,16 @@
         <v>117.691580641443</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>99.56522744598161</v>
+        <v>99.18786119083759</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>87.0401219404262</v>
+        <v>84.22806806837229</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>138.753438025449</v>
+        <v>131.826741429863</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>238.99954056515</v>
+        <v>227.958201246033</v>
       </c>
       <c r="I45" s="2" t="n"/>
     </row>
@@ -8643,16 +8716,16 @@
         <v>0</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>0.3773662551440111</v>
+        <v>0</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>2.812053872053909</v>
+        <v>0</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>6.92669659558598</v>
+        <v>0</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>11.04133931911699</v>
+        <v>0</v>
       </c>
       <c r="I46" s="2" t="n"/>
     </row>
@@ -8827,7 +8900,7 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>39.0619724751706</v>
+        <v>41.8740263472245</v>
       </c>
       <c r="D54" s="2" t="n"/>
       <c r="E54" s="2" t="n"/>
@@ -8848,7 +8921,7 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>-33.2398780595738</v>
+        <v>-36.0519319316277</v>
       </c>
       <c r="D55" s="2" t="n"/>
       <c r="E55" s="2" t="n"/>
@@ -8913,7 +8986,7 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>87.0401219404262</v>
+        <v>84.22806806837229</v>
       </c>
       <c r="D58" s="2" t="n"/>
       <c r="E58" s="2" t="n"/>
@@ -9059,16 +9132,16 @@
         <v>-5.36501172129409</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>-4.82838767297759</v>
+        <v>-4.91025301987502</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>-2.36820322078252</v>
+        <v>-2.69802276504026</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>3.57869294486578</v>
+        <v>3.03278502342309</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>4.72569908457296</v>
+        <v>4.13475145036218</v>
       </c>
       <c r="I64" s="2" t="n"/>
     </row>
@@ -9090,16 +9163,16 @@
         <v>0.888124307888594</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>0.773801380995813</v>
+        <v>0.770845036748019</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.867395652649717</v>
+        <v>0.851667231837521</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>1.25745745936383</v>
+        <v>1.21139975474192</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>1.35500391456511</v>
+        <v>1.30275729846968</v>
       </c>
       <c r="I65" s="2" t="n"/>
     </row>
@@ -9121,16 +9194,16 @@
         <v>-2.58841935855733</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>-18.1263531954611</v>
+        <v>-18.5037194506051</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>-12.5251055055554</v>
+        <v>-14.9597931224653</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>37.7422595275447</v>
+        <v>33.0104203954834</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>59.0829328672689</v>
+        <v>53.1167009181481</v>
       </c>
       <c r="I66" s="2" t="n"/>
     </row>
@@ -9158,10 +9231,10 @@
         <v>0</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>13.9710565574776</v>
+        <v>14.5882529660074</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>41.1631696724328</v>
+        <v>43.0147588980221</v>
       </c>
       <c r="I67" s="2" t="n"/>
     </row>
@@ -9180,7 +9253,7 @@
         <v>2029</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>39.0619724751706</v>
+        <v>41.8740263472245</v>
       </c>
       <c r="E68" s="2" t="n">
         <v>0</v>
@@ -9189,7 +9262,7 @@
         <v>0</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>87.0401219404262</v>
+        <v>84.22806806837229</v>
       </c>
       <c r="H68" s="2" t="n"/>
       <c r="I68" s="2" t="n"/>
@@ -9212,16 +9285,16 @@
         <v>-5.36501172129409</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>-4.82838767297759</v>
+        <v>-4.91025301987502</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>-2.36820322078252</v>
+        <v>-2.69802276504026</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>4.88495712551547</v>
+        <v>4.3889652956446</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>8.719885378457599</v>
+        <v>8.251760587277341</v>
       </c>
       <c r="I69" s="2" t="n"/>
     </row>
@@ -9243,16 +9316,16 @@
         <v>0.888124307888594</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0.773801380995813</v>
+        <v>0.770845036748019</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.867395652649717</v>
+        <v>0.851667231837521</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>1.35143240004448</v>
+        <v>1.30593206570996</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>1.65505513332769</v>
+        <v>1.60421545841741</v>
       </c>
       <c r="I70" s="2" t="n"/>
     </row>
@@ -9274,16 +9347,16 @@
         <v>-2.58841935855733</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>-18.1263531954611</v>
+        <v>-18.5037194506051</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>-12.5251055055554</v>
+        <v>-14.9597931224653</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>49.4379865399318</v>
+        <v>45.222827064666</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>103.720536976805</v>
+        <v>99.7621802103551</v>
       </c>
       <c r="I71" s="2" t="n"/>
     </row>
@@ -9311,10 +9384,10 @@
         <v>0</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>13.9710565574776</v>
+        <v>14.5882529660074</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>41.1631696724328</v>
+        <v>43.0147588980221</v>
       </c>
       <c r="I72" s="2" t="n"/>
     </row>
@@ -9333,7 +9406,7 @@
         <v>2029</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>39.0619724751706</v>
+        <v>41.8740263472245</v>
       </c>
       <c r="E73" s="2" t="n">
         <v>0</v>
@@ -9342,7 +9415,7 @@
         <v>0</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>87.0401219404262</v>
+        <v>84.22806806837229</v>
       </c>
       <c r="H73" s="2" t="n"/>
       <c r="I73" s="2" t="n"/>
@@ -9365,16 +9438,16 @@
         <v>-5.36501172129409</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>-4.82838767297759</v>
+        <v>-4.91025301987502</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>-2.36820322078252</v>
+        <v>-2.69802276504026</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>6.19122130616515</v>
+        <v>5.74514556786612</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>12.7140716723422</v>
+        <v>12.3687697241925</v>
       </c>
       <c r="I74" s="2" t="n"/>
     </row>
@@ -9396,16 +9469,16 @@
         <v>0.888124307888594</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.773801380995813</v>
+        <v>0.770845036748019</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.867395652649717</v>
+        <v>0.851667231837521</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>1.44540734072513</v>
+        <v>1.40046437667801</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>1.95510635209028</v>
+        <v>1.90567361836515</v>
       </c>
       <c r="I75" s="2" t="n"/>
     </row>
@@ -9427,16 +9500,16 @@
         <v>-2.58841935855733</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>-18.1263531954611</v>
+        <v>-18.5037194506051</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>-12.5251055055554</v>
+        <v>-14.9597931224653</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>61.1337135523189</v>
+        <v>57.4352337338487</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>148.358141086342</v>
+        <v>146.407659502562</v>
       </c>
       <c r="I76" s="2" t="n"/>
     </row>
@@ -9464,10 +9537,10 @@
         <v>0</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>13.9710565574776</v>
+        <v>14.5882529660074</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>41.1631696724328</v>
+        <v>43.0147588980221</v>
       </c>
       <c r="I77" s="2" t="n"/>
     </row>
@@ -9486,7 +9559,7 @@
         <v>2029</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>39.0619724751706</v>
+        <v>41.8740263472245</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>0</v>
@@ -9495,7 +9568,7 @@
         <v>0</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>87.0401219404262</v>
+        <v>84.22806806837229</v>
       </c>
       <c r="H78" s="2" t="n"/>
       <c r="I78" s="2" t="n"/>
@@ -9551,22 +9624,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>U2 新法：付款上限的年度形狀</t>
+          <t>U2 新法：付款路徑</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>年上限＝『最高 86』×MW 比例 ÷ Σ 爬坡權重 × 當年權重（即 v0.1.1 的付款時程）</t>
+          <t>chat 端更正：付款路徑不變＝『最高 86』按 MW 比例（460:350）分攤、÷ Σ 爬坡權重 × 當年權重（v0.1.1／v0.1.2 的路徑）；只把供給 GW 改回揭露容量</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>平均分攤（86 ÷ 期間，不爬坡）</t>
+          <t>按兩約公告金額比例（45:35）分攤（工作單文字）</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>上限在基準下不約束（Nscale 揭露容量付款 5.5 &lt; 上限 8.9），兩種形狀結果相同</t>
+          <t>由比例推得：Nscale 年付款約 −1.0%（8.88 → 約 8.80）、Lambda 約 +1.3%；對差額的影響未另行重算。未採用，因工作單同一句要求『v0.1.2 付款路徑不變』</t>
         </is>
       </c>
     </row>
@@ -9588,7 +9661,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2030 以前相同；2033–2034 不在模型期間</t>
+          <t>2030 以前相同</t>
         </is>
       </c>
     </row>
@@ -9600,7 +9673,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Inputs u2_method（INP_187）＝1；0 可重現 v0.1.1／v0.1.2</t>
+          <t>Inputs u2_method（INP_187）＝1；0 且 u2_switch＝1 重現 v0.1.1／v0.1.2</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -9610,7 +9683,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2030 差額 11.14 → 12.13</t>
+          <t>2030 差額 11.14 → 11.60；成本不變</t>
         </is>
       </c>
     </row>
@@ -9676,7 +9749,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2030 追加實付 41.2（基準合約付款 88.1 的 47%，含 2029 批滿載＋2030 批半載）</t>
+          <t>2030 追加實付 43.0（基準合約付款 92.3 的 47%）</t>
         </is>
       </c>
     </row>
